--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -878,7 +878,7 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>A · Cloud Run function (deploy.sh → gcloud run deploy --function, Scheduler OIDC, Secret Manager, BigQuery MERGE)</t>
+          <t>A · Cloud Run function (deploy.sh → gcloud run deploy --function, Scheduler OIDC, Secret Manager, BigQuery MERGE) — operator surfaces: Cloud Shell runbook docs/RUNBOOK_CLOUD_SHELL.md and the Vertex AI Workbench notebook notebooks/cloudbq_deploy_and_witness.ipynb (same deploy.sh)</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
@@ -1039,9 +1039,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>`deploy.sh secret`: Secret Manager hubspot-token (create or versions add from $HUBSPOT_TOKEN in the shell, never in .env), accessor
-for the SA; `deploy.sh deploy` pins --set-secrets HUBSPOT_TOKEN=hubspot-token:${SECRET_VERSION} (empty → newest enabled version
-number resolved at deploy time, never the literal "latest"); optional DELIVERY_WEBHOOK_TOKEN from $DELIVERY_WEBHOOK_TOKEN_SECRET.</t>
+          <t>`deploy.sh secret`: Secret Manager hubspot-token (create or versions add from $HUBSPOT_TOKEN typed into the shell — never in .env, check-env refuses it), accessor for the SA; prints the version NUMBER; `deploy.sh deploy` pins --set-secrets HUBSPOT_TOKEN=hubspot-token:${SECRET_VERSION} (empty → newest enabled version number resolved with value(name.basename()) at deploy time, never the literal "latest" and never the resource path, R47); optional DELIVERY_WEBHOOK_TOKEN from $DELIVERY_WEBHOOK_TOKEN_SECRET.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1077,8 +1075,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>deploy.sh refuses nothing here but resolves the version number (read); deploy_job.sh refuses a missing version (DRYRUN=1 run);
-secrets.sh DRYRUN=1 lists the three secrets. Secrets created: not yet — first authenticated run.</t>
+          <t>deploy.sh secret_version() resolves the version NUMBER with value(name.basename()) — value(name) returned projects/…/versions/N and would have been rejected by --set-secrets (R47, fixed 574e954, DRYRUN=1 prints the corrected command); deploy_job.sh refuses a missing version (DRYRUN=1 run); secrets.sh DRYRUN=1 lists the three secrets. Secrets created: not yet — first authenticated run.</t>
         </is>
       </c>
     </row>
@@ -1095,9 +1092,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>`deploy.sh invoker`: two Cloud Scheduler HTTP jobs new-deals-SEALSQ "0 7 * * 1" and new-deals-ICALPS "20 7 * * 1" --time-zone
-Europe/Zurich, GET $URL?entity=…, --oidc-service-account-email new-deals-fn@, --oidc-token-audience $URL, --attempt-deadline 600s,
---max-retry-attempts 3, create-or-update, created PAUSED; `deploy.sh enable` resumes.</t>
+          <t>`deploy.sh invoker`: two Cloud Scheduler HTTP jobs new-deals-SEALSQ "0 7 * * 1" and new-deals-ICALPS "20 7 * * 1" --time-zone Europe/Zurich, GET $URL?entity=…, --oidc-service-account-email new-deals-fn@, --oidc-token-audience $URL, --attempt-deadline 600s, --max-retry-attempts 3, create-or-update, created PAUSED; `deploy.sh enable` resumes only PAUSED jobs and `pause` only ENABLED ones (idempotent, R49). Cloud Scheduler is offered in europe-west6 (locations page, 2026-10-16).</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1551,9 +1546,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>`deploy.sh dry`: ?dry_run=1 for both entities; main.py builds the BigQuery client in dry mode, reads watermark + warehouse twins,
-skips MERGE, history, watermark, run row and delivery; payload carries dry_run: true; the step asserts rows_written == 0 and prints
-rows/dup/hot/window. Nothing is written; the lease is not taken.</t>
+          <t>`deploy.sh dry`: ?dry_run=1 for both entities; main.py builds the BigQuery client in dry mode, reads watermark + warehouse twins, skips MERGE, history, watermark, run row and delivery; payload carries dry_run: true; the step asserts rows_written == 0 and prints rows/dup/hot/window. curl -sSf: an HTTP 403 (caller lacks run.invoker) or 409 (lease held) fails the gate instead of passing a JSON error as a payload (R50). Nothing is written; the lease is not taken. Same gate from the Workbench notebook (cells 3.8 and 4.6) and the Cloud Shell runbook Phase 7.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1609,9 +1602,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>`deploy.sh replay ENTITY FROM_ISO`: UPDATE report_state SET watermark = TIMESTAMP 'FROM', updated_at = now WHERE report_id =
-'NEW_DEALS_&lt;entity&gt;' then `deploy.sh run ENTITY`; MERGE dedupes; day1_* frozen so historical scores survive; new_deals_history slice
-for the new run_ts; the first run with no watermark looks back FIRST_RUN_DAYS.</t>
+          <t>`deploy.sh replay ENTITY FROM_ISO`: UPDATE report_state SET watermark = TIMESTAMP 'FROM', updated_at = now WHERE report_id = 'NEW_DEALS_&lt;entity&gt;' then `deploy.sh run ENTITY`; MERGE dedupes; day1_* frozen so historical scores survive; new_deals_history slice for the new run_ts; the first run with no watermark looks back FIRST_RUN_DAYS. replay is the idempotency check of the runbook (FROM = window.query_start of the first run); a second `run` opens the next window instead (R52).</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1725,9 +1716,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Private service (--no-allow-unauthenticated); `deploy.sh invoker` binds roles/run.invoker to new-deals-fn@ for the Scheduler's OIDC
-token (humans need run.invoker for `deploy.sh dry`/`run`); SA roles: bigquery.jobUser (project), dataEditor (dataset DCL),
-secretmanager.secretAccessor (hubspot-token); HubSpot read-only private app.</t>
+          <t>Private service (--no-allow-unauthenticated); `deploy.sh invoker` binds roles/run.invoker to new-deals-fn@ for the Scheduler's OIDC token; humans need run.invoker for `deploy.sh dry`/`run` (Owner/Editor have it); when gcloud's active account is a service account (Workbench instance, VM) `invoke` mints the ID token with --audiences $URL, which Cloud Run requires for service accounts (R48); SA roles: bigquery.jobUser (project), dataEditor (dataset DCL — on the whole dataset, e.g. mrload), secretmanager.secretAccessor (hubspot-token); HubSpot read-only private app.</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1976,7 +1965,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>A · Cloud Run function (deploy.sh → gcloud run deploy --function, Scheduler OIDC, Secret Manager, BigQuery MERGE) — cell</t>
+          <t>A · Cloud Run function (deploy.sh → gcloud run deploy --function, Scheduler OIDC, Secret Manager, BigQuery MERGE) — operator surfaces: Cloud Shell runbook docs/RUNBOOK_CLOUD_SHELL.md and the Vertex AI Workbench notebook notebooks/cloudbq_deploy_and_witness.ipynb (same deploy.sh) — cell</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -2181,7 +2170,7 @@
       <c r="C6" s="4" t="inlineStr"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>HUBSPOT_TOKEN=… deploy.sh secret — hubspot-token create or versions add, secretAccessor for the SA; prints the version to pin in .env SECRET_VERSION</t>
+          <t>IFS= read -rsp … HUBSPOT_TOKEN; HUBSPOT_TOKEN="$HUBSPOT_TOKEN" deploy.sh secret — hubspot-token create or versions add (a version per run), secretAccessor for the SA; prints the version NUMBER (value(name.basename()), R47) to pin in .env SECRET_VERSION (optional: deploy resolves the newest enabled number)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2308,7 +2297,7 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>deploy.sh dry — curl $URL?entity=SEALSQ&amp;dry_run=1 and ICALPS with an identity token; asserts rows_written == 0 and dry_run true; prints rows/dup/hot/window</t>
+          <t>deploy.sh dry — curl -sSf $URL?entity=SEALSQ&amp;dry_run=1 and ICALPS with the caller's identity token (a service account's carries audience = $URL, R48); asserts rows_written == 0 and dry_run true; an HTTP 403 (caller lacks run.invoker) or 409 (lease held) fails the step (R50); prints rows/dup/hot/window</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -2353,7 +2342,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>deploy.sh run SEALSQ then deploy.sh run ICALPS — one live window run each; prints report_id, run_timestamp, window, row_count, rows_written, duplicate_suspects, day1_hot</t>
+          <t>deploy.sh run SEALSQ then deploy.sh run ICALPS — one live window run each (the first without a watermark looks back FIRST_RUN_DAYS); prints report_id, run_timestamp, window, row_count, rows_written, duplicate_suspects, day1_hot; refuses an error payload or one without rows_written (R50); each run moves the watermark — the idempotency check is step 13 replay, not a second run (R52)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2398,7 +2387,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>deploy.sh enable — gcloud scheduler jobs resume new-deals-SEALSQ / -ICALPS</t>
+          <t>deploy.sh enable — gcloud scheduler jobs resume new-deals-SEALSQ / -ICALPS, only those in state PAUSED (idempotent, R49); pause likewise only ENABLED jobs</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2525,7 +2514,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>deploy.sh replay SEALSQ 2026-09-01T00:00:00Z — UPDATE report_state SET watermark = TIMESTAMP '…' WHERE report_id = 'NEW_DEALS_SEALSQ' then deploy.sh run SEALSQ</t>
+          <t>deploy.sh replay SEALSQ FROM_ISO — UPDATE report_state SET watermark = TIMESTAMP 'FROM' WHERE report_id = 'NEW_DEALS_SEALSQ' then deploy.sh run SEALSQ; the runbook's idempotency check with FROM = window.query_start of the first run (R52): probe counts unchanged</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2565,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4316,6 +4305,265 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>R47</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Pre-run review (2026-10-16): deploy.sh secret_version() read the Secret Manager version with --format value(name), i.e. projects/N/secrets/hubspot-token/versions/V; `deploy` would have passed that path to --set-secrets and Cloud Run rejects it</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>gcloud's own table uses name.basename(); value(name) is the raw resource name.</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>deploy.sh lines 86 and 91 use --format 'value(name.basename())' (the version number); the `secret` hint prints the number.</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>fixed in 574e954 — DRYRUN=1 deploy.sh deploy prints value(name.basename()); live deploy not yet — first authenticated run</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>R48</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Pre-run review: from a Vertex AI Workbench instance or any VM whose gcloud account is a service account, `gcloud auth print-identity-token` carries gcloud's client id as audience; Cloud Run requires the service URL for service-account tokens, so `dry`/`run` would fail with 401/403 on that surface</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>deploy.sh invoke() minted the token without --audiences; only a person's token is accepted as is.</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>invoke() reads the active account; a *.gserviceaccount.com account gets --audiences "$u"; the notebook's cell 4.6 chooses by ADC type (user → gcloud token, service account → fetch_id_token(audience = URL)).</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>fixed in 574e954 / e88c27a (code read; DRYRUN=1 prints the account lookup); live call not yet — first authenticated run</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>R49</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Pre-run review: `deploy.sh enable` after a successful enable exited non-zero — the Scheduler API refuses to resume a job that is not PAUSED; same for pause; contradicted the header's "re-running a step is safe"</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>resume/pause were unconditional.</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>enable() resumes only jobs in state PAUSED, pause() only ENABLED ones (job_state helper); the header names the steps that are not no-ops (secret adds a version, run moves the watermark).</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>fixed in 574e954 (DRYRUN=1 enable/pause rehearsed); live not yet — first authenticated run</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>R50</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Pre-run review: `run` could not tell success from the function's 409 "lease held" or any JSON error body — curl without -f printed {"report_id": …} and exited 0 while nothing was written; `dry` would die with a JSONDecodeError on a 403 instead of the status</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>invoke() used curl -sS; live() printed whatever keys were present.</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>curl -sSf (HTTP 4xx/5xx fail the step with the status); live() asserts no "error" key and a rows_written key; the runbook lists the status → cause table (403 caller lacks run.invoker, 500 + HubSpot 401 in logs, 500 + Not found table, 409 lease).</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>fixed in 574e954 (bash -n, DRYRUN=1 dry/run); live not yet — first authenticated run</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>R51</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Pre-run review: tests/test_hot_score.py emit_sql() wrote bare NULLs; a struct column that is NULL in every row of the UNNEST is typed INT64, so SAFE_CAST(… AS TIMESTAMP) and the STRING UDF parameters fail — impossible on the 15 golden vectors, likely on live deals (notes_last_updated, revenue_state often all NULL)</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>A C</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>BigQuery supertype rule for NULL-only literals; sql_literal() also left backslashes unescaped.</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>sql_literal(v, typ) emits CAST(NULL AS STRING|FLOAT64|BOOL) and escapes backslashes; tests/hot_score_vectors.sql regenerated; the notebook's live-parity cell reuses emit_sql unchanged.</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>fixed in 574e954 (python3 tests/test_hot_score.py: constants OK · python vectors OK · JS port OK); the SQL itself not yet executed — first authenticated run</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>R52</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Operator runbook draft: "BQ_LOCATION stays EU, fine for europe-west6" (the BigQuery location is independent of the Cloud Run region — it must equal the existing dataset's location), a second `run SEALSQ` as the idempotency check (each run moves the watermark, so it opens the next window), a 403 on `dry` attributed to the `invoker` step (dry uses the operator's identity), portal 49610528 vs 9201667</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>The runbook was drafted from the sequence without the state model; the portal id came from an earlier draft.</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>docs/RUNBOOK_CLOUD_SHELL.md — Phase 2 checks `bq show` location == BQ_LOCATION (mrload was created in EU by mir-load run_pass1.sh); Phase 7 uses `replay SEALSQ "$FROM"` with FROM = window.query_start of the first run; 403 → the caller''s run.invoker; portal 9201667 confirmed as the hub id of the connected HubSpot account.</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>this commit (docs); PASS1_SEQUENCE.md corrected the same way in e88c27a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>R53</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Operator runbook draft: Phase 3 ran python3 tests/*.py in Cloud Shell, whose Python has no functions-framework / google-cloud-bigquery / flask, so the offline rehearsal would have failed on import</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>L0</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>main.py imports functions_framework at import time; the tests import main.</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>a virtualenv in $HOME (persists in Cloud Shell): python3 -m venv ~/.venvs/cloudbq &amp;&amp; pip install -r cloud_function_new_deals/requirements.txt pyyaml pytest; the Workbench notebook installs the same into its kernel.</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>this commit (docs); the CI job installs the same requirements before pytest (green)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4327,7 +4575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4350,7 +4598,7 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>A · Cloud Run function (deploy.sh → gcloud run deploy --function, Scheduler OIDC, Secret Manager, BigQuery MERGE) — cell</t>
+          <t>A · Cloud Run function (deploy.sh → gcloud run deploy --function, Scheduler OIDC, Secret Manager, BigQuery MERGE) — operator surfaces: Cloud Shell runbook docs/RUNBOOK_CLOUD_SHELL.md and the Vertex AI Workbench notebook notebooks/cloudbq_deploy_and_witness.ipynb (same deploy.sh) — cell</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
@@ -4550,6 +4798,33 @@
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>XLSX rows == row_count == rows of new_deals_last_7d for the same window; a zero-row week sends the text-only "no new deals" mail (B1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>probe from two operator surfaces (lane A)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>the two `probe` queries run by deploy.sh (bq CLI, Cloud Shell runbook Phase 7) and by the Workbench notebook cell 4.5 (BigQuery Python client) against the same tables</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>deploy.sh probe — SELECT entity, COUNT(*) n, COUNTIF(day1_hot_flag) hot, COUNTIF(duplicate_suspect) dup, MIN(createdate), MAX(createdate) FROM new_deals GROUP BY entity; last 10 new_deals_runs</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>n/a — same lane, two surfaces: notebooks/cloudbq_deploy_and_witness.ipynb cell 4.5 runs the identical SQL through bigquery.Client and prints job id, bytes processed, slot ms</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>identical rows and counts from both surfaces (job ids differ); the notebook additionally shows hot_score_v1 reproducing the 15 golden vectors and main.hot_score agreeing with it</t>
         </is>
       </c>
     </row>

--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -1150,7 +1150,9 @@
         <is>
           <t>main.py read_watermark(): SELECT watermark FROM report_state WHERE report_id = 'NEW_DEALS_&lt;entity&gt;' (default now − FIRST_RUN_DAYS=7);
 HubSpot POST /crm/v3/objects/deals/search createdate GTE watermark − OVERLAP_MINUTES(5) AND LT run_ts, PROPS (29 properties), sort
-createdate ASC, 200/page; deals filtered by ENTITIES[entity].pipelines, the rest kept as duplicate candidates ("others").</t>
+createdate ASC, 200/page; deals filtered by ENTITIES[entity].pipelines, the rest kept as duplicate candidates ("others"). Pass 3
+phase 1: the whole search result (in_scope per deal) and the pipeline/stage/owner maps land in deals_raw / labels_raw keyed by
+(run_ts, entity, orchestrator) before shape() — load first, delete-older second; non-fatal (data_gaps raw_landing_failed); dry does not land.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1164,7 +1166,10 @@
         <is>
           <t>No HubSpot search: sql/new_deals_weekly.sql selects deals_synced_v1 WHERE createdate in [run_ts − 14 d, run_ts) AND pipeline_id IN
 ${PIPELINES} after a freshness guard (RAISE + ABORTED run row when MAX(lastmodified) &lt; run_ts − 36 h). Source = scheduled full-refresh
-sync (DTS, Preview) into $SYNC_DATASET.$SYNC_DEALS_TABLE read through the adapter view. No event mode.</t>
+sync (DTS, Preview) into $SYNC_DATASET.$SYNC_DEALS_TABLE read through the adapter view. No event mode. Pass 3 phase 1: after the guard
+and before the transaction, sql/land_raw.sql (spliced by scheduled_query.sh) lands the 90-day set from the sync TABLE with HubSpot
+property names (TO_JSON of the 29 PROPS) and the labels, same key and same INSERT-then-DELETE-older order as A; sql/backfill_raw.sh
+lands it once per entity with orchestrator = backfill at cut-over.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1659,7 +1664,8 @@
           <t>main.py write_run(): one row per run in hubspot.new_deals_runs (run_ts, entity, mode, dry_run, orchestrator = 'cloud-run-function',
 window, row_count, rows_written, duplicate_suspects, day1_hot, status OK | OK_DELIVERY_FAILED | FAILED, error, duration_ms) — also in
 the exception path; write_history(): the run's rows appended to hubspot.new_deals_history (slice replaced by run_ts/entity/orchestrator);
-JSON log line "run complete".</t>
+JSON log line "run complete". Pass 3 phase 1: new_deals_runs.data_gaps ARRAY&lt;STRING&gt; names what the run could not read or compute
+(raw_landing_failed, dedup_scope_batch_only, event_no_window); deals_raw / labels_raw hold the run's inputs as delivered (JSON).</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1674,7 +1680,9 @@
           <t>sql/new_deals_weekly.sql writes new_deals_history and new_deals_runs (orchestrator = 'bigquery-scheduled-query', ABORTED row on a
 stale sync) inside the transaction; writeback/index.mjs writes hubspot.writeback_log (run_ts, deal_id, new/previous values, status
 OK | ERROR | DRY, http_status, error, dry_run); plus `bq ls --transfer_run` history. DDL: cloud_function_new_deals/bigquery_schema.sql
-(new_deals_runs) + sql/audit_tables.sql (new_deals_history, writeback_log).</t>
+(new_deals_runs) + sql/audit_tables.sql (new_deals_history, writeback_log). Pass 3 phase 1: data_gaps on the runs row (sync_stale on
+the ABORTED row; source_detail_unavailable; raw_backfilled_from_current_sync when run_time is older than an hour) and the deals_raw /
+labels_raw slices from sql/land_raw.sql, kept even when the transaction fails. DDL for both raw tables: bigquery_schema.sql.</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -2554,7 +2562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4564,6 +4572,43 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>R54</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Pass 3 finding: both lanes reconstruct their OUTPUTS per run (new_deals_runs, new_deals_history) but never persist their INPUTS — the HubSpot search result is consumed by shape() and discarded, six of the ten hot-score inputs are columns of no table, lane C computes a TEMP table from a view over a full-refresh sync — so day1_hot_score, duplicate_of, the label strings and the delivered report of a past run cannot be recomputed from BigQuery</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>A C</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>No run_ts-keyed landing of what each run computed from; an orchestrator would sequence nodes without persisting the missing one.</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Phase 1 (this commit, docs/PASS3_RAW_ROOT.md): deals_raw (properties JSON as delivered, in_scope, createdate, pipeline_id) and labels_raw keyed by (run_ts, entity, orchestrator) like new_deals_history; lane A lands the whole search before shape() (non-fatal, named in new_deals_runs.data_gaps), lane C lands its 90-day set from the sync table before its transaction (sql/land_raw.sql); sql/backfill_raw.sh fills the duplicate horizon at cut-over. Phase 2: one SQL implementation over the root (adapter view, table function, procedure). Phase 3: the function calls the procedure; shape()/hot_score() become test oracles; n8n B2 retired.</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_main_offline.py (7 root tests: order, slice replacement, JSON dict, dry, failure named, clean gaps, event); rendered scripts (DRYRUN=1 sql/scheduled_query.sh, DRYRUN=1 sql/backfill_raw.sh); acceptance SQL in docs/PASS3_RAW_ROOT.md after the first live run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4575,7 +4620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4828,6 +4873,33 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>after first live run (pass 3 phase 1 — the root)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>every (run_ts, entity, orchestrator, deal_id) of new_deals_history has its row in deals_raw; the JSON carries the property names; data_gaps per run</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>bq query 'SELECT COUNT(*) FROM `$PROJECT.hubspot.new_deals_history` h LEFT JOIN `$PROJECT.hubspot.deals_raw` r USING (run_ts, entity, orchestrator, deal_id) WHERE r.deal_id IS NULL AND h.orchestrator = ''cloud-run-function'' AND h.run_ts &gt;= TIMESTAMP ''&lt;cut-over&gt;'''</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>C: same query with orchestrator = 'bigquery-scheduled-query' (and 'backfill' for the one-time landing); both: SELECT orchestrator, COUNTIF(JSON_VALUE(properties, '$.pipeline') IS NULL) FROM `$PROJECT.hubspot.deals_raw` GROUP BY 1; SELECT run_ts, entity, orchestrator, status, data_gaps FROM `$PROJECT.hubspot.new_deals_runs` ORDER BY run_ts DESC</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>0 missing rows for both orchestrators; 0 NULL pipelines in the JSON; data_gaps [] on a clean lane-A run, [source_detail_unavailable] on a clean lane-C run; raw slices with no OK runs row list only failed runs (kept by design)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -1168,7 +1168,8 @@
 ${PIPELINES} after a freshness guard (RAISE + ABORTED run row when MAX(lastmodified) &lt; run_ts − 36 h). Source = scheduled full-refresh
 sync (DTS, Preview) into $SYNC_DATASET.$SYNC_DEALS_TABLE read through the adapter view. No event mode. Pass 3 phase 1: after the guard
 and before the transaction, sql/land_raw.sql (spliced by scheduled_query.sh) lands the 90-day set from the sync TABLE with HubSpot
-property names (TO_JSON of the 29 PROPS) and the labels, same key and same INSERT-then-DELETE-older order as A; sql/backfill_raw.sh
+property names (TO_JSON of 28 of the 29 PROPS: hs_object_source_detail_1 waits for the first transfer to confirm the column) and the labels,
+same key and same INSERT-then-DELETE-older order as A, inside a BEGIN … EXCEPTION block that names raw_landing_failed; sql/backfill_raw.sh
 lands it once per entity with orchestrator = backfill at cut-over.</t>
         </is>
       </c>
@@ -1680,7 +1681,7 @@
           <t>sql/new_deals_weekly.sql writes new_deals_history and new_deals_runs (orchestrator = 'bigquery-scheduled-query', ABORTED row on a
 stale sync) inside the transaction; writeback/index.mjs writes hubspot.writeback_log (run_ts, deal_id, new/previous values, status
 OK | ERROR | DRY, http_status, error, dry_run); plus `bq ls --transfer_run` history. DDL: cloud_function_new_deals/bigquery_schema.sql
-(new_deals_runs) + sql/audit_tables.sql (new_deals_history, writeback_log). Pass 3 phase 1: data_gaps on the runs row (sync_stale on
+(new_deals_runs, new_deals_history) + sql/audit_tables.sql (writeback_log). Pass 3 phase 1: data_gaps on the runs row (sync_stale on
 the ABORTED row; source_detail_unavailable; raw_backfilled_from_current_sync when run_time is older than an hour) and the deals_raw /
 labels_raw slices from sql/land_raw.sql, kept even when the transaction fails. DDL for both raw tables: bigquery_schema.sql.</t>
         </is>
@@ -1699,8 +1700,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>None needed for the tables; `deploy.sh probe` is the shared query. R44: new_deals_history is created only by sql/audit_tables.sql —
-apply it before any live run of A or B2 (or fold it into bigquery_schema.sql).</t>
+          <t>None needed for the tables; `deploy.sh probe` is the shared query. R44 (closed): new_deals_history now lives in bigquery_schema.sql, so
+`deploy.sh tables` creates it; sql/audit_tables.sql keeps writeback_log.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -4580,7 +4581,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Pass 3 finding: both lanes reconstruct their OUTPUTS per run (new_deals_runs, new_deals_history) but never persist their INPUTS — the HubSpot search result is consumed by shape() and discarded, six of the ten hot-score inputs are columns of no table, lane C computes a TEMP table from a view over a full-refresh sync — so day1_hot_score, duplicate_of, the label strings and the delivered report of a past run cannot be recomputed from BigQuery</t>
+          <t>Pass 3 finding: both lanes reconstruct their OUTPUTS per run (new_deals_runs, new_deals_history) but never persist their INPUTS — the HubSpot search result is consumed by shape() and discarded, six of the eleven hot-score inputs are columns of no table, lane C computes a TEMP table from a view over a full-refresh sync — so day1_hot_score, duplicate_of, the label strings and the delivered report of a past run cannot be recomputed from BigQuery</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4605,7 +4606,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>tests/test_main_offline.py (7 root tests: order, slice replacement, JSON dict, dry, failure named, clean gaps, event); rendered scripts (DRYRUN=1 sql/scheduled_query.sh, DRYRUN=1 sql/backfill_raw.sh); acceptance SQL in docs/PASS3_RAW_ROOT.md after the first live run</t>
+          <t>tests/test_main_offline.py (11 root tests: order, slice replacement, JSON dict, dry, failure named, clean gaps as an ArrayQueryParameter, event with the delete scoped to its deal, strict replacement across two landings, labels-only failure, time-boxed jobs, runs row kept on an un-migrated table); rendered scripts (DRYRUN=1 sql/scheduled_query.sh, DRYRUN=1 sql/backfill_raw.sh); review follow-ups folded in (deploy.sh deploy applies tables first, LAND_TIMEOUT_S, lane-C landing non-fatal, IFNULL in_scope, stringify_wide_numbers, splice asserted); acceptance SQL in docs/PASS3_RAW_ROOT.md after the first live run</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4897,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>0 missing rows for both orchestrators; 0 NULL pipelines in the JSON; data_gaps [] on a clean lane-A run, [source_detail_unavailable] on a clean lane-C run; raw slices with no OK runs row list only failed runs (kept by design)</t>
+          <t>0 missing rows for both orchestrators; 0 NULL pipelines in the JSON; data_gaps [] on a clean lane-A run once new_deals holds name_key rows from the last 90 days ([dedup_scope_batch_only] on the first run of an empty warehouse or when recent_names() failed — main.py `if not known`; [raw_slice_replaced] when the key was re-landed); [source_detail_unavailable] on a clean lane-C run (plus raw_backfilled_from_current_sync when run_time is older than an hour); raw slices with no OK runs row = failed or undelivered runs plus the backfill slices, which have no runs row by design</t>
         </is>
       </c>
     </row>

--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -1170,7 +1170,8 @@
 and before the transaction, sql/land_raw.sql (spliced by scheduled_query.sh) lands the 90-day set from the sync TABLE with HubSpot
 property names (TO_JSON of 28 of the 29 PROPS: hs_object_source_detail_1 waits for the first transfer to confirm the column) and the labels,
 same key and same INSERT-then-DELETE-older order as A, inside a BEGIN … EXCEPTION block that names raw_landing_failed; sql/backfill_raw.sh
-lands it once per entity with orchestrator = backfill at cut-over.</t>
+lands it once per entity with orchestrator = backfill at cut-over. Phase 2: the landing precedes the CALL of new_deals_batch (the
+script has no transaction of its own any more).</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1226,8 +1227,9 @@
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>scoring/hot_score_v1.sql → persistent UDF `$PROJECT.$DATASET.hot_score_v1(...) RETURNS STRUCT&lt;score, hot, raw&gt;` applied by sql/apply.sh;
-called by sql/new_deals_weekly.sql (day1_hot_score / day1_hot_flag) and sql/hot_deals_v1.sql (hot_score_v1 / hot_flag_v1).
-tests/hot_score_vectors.sql is the bq check generated from the same vectors.</t>
+called by the pass-3 table function new_deals_batch_rows (sql/deals_landed_v1.sql; day1_hot_score / day1_hot_flag, run_ts as "now")
+and sql/hot_deals_v1.sql (hot_score_v1 / hot_flag_v1). tests/hot_score_vectors.sql is the bq check generated from the same vectors;
+tests/pass3_batch_vectors.sql runs the same 15 vectors through the root → view → table function in a dev dataset.</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1282,9 +1284,11 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>sql/new_deals_weekly.sql: name_key = SUBSTR(REGEXP_REPLACE(LOWER(COALESCE(NULLIF(TRIM(final_customer),''), REGEXP_EXTRACT(dealname,
-r'^[^-/|(]*'))), r'[^a-z0-9]', ''), 1, 40); dups = self-join of the window against every synced deal created in the last 90 days
-(any pipeline, any entity), STRING_AGG ordered by createdate; labels from owners_synced_v1 / pipelines_synced_v1 / pipeline_stages_synced_v1.</t>
+          <t>Pass 3 phase 2 — sql/deals_landed_v1.sql: name_key = IFNULL(SUBSTR(REGEXP_REPLACE(LOWER(COALESCE(NULLIF(TRIM(final_customer),''),
+REGEXP_EXTRACT(dealname, r'^[^-/|(]*'))), r'[^a-z0-9]', ''), 1, 40), '') computed once in the view; new_deals_batch_rows: dups =
+the window against every deal the ROOT knows as of run_ts (any entity, any orchestrator, in-scope or not, 90-day horizon, latest
+observation per deal_id), STRING_AGG ordered by createdate, deal_id; labels from the slice's labels_raw rows (id as fallback).
+Before phase 2 the weekly script did the same over the synced views.</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1339,9 +1343,11 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>sql/new_deals_weekly.sql: CREATE TEMP TABLE batch … ; MERGE `new_deals` t USING batch s ON t.deal_id = s.deal_id WHEN MATCHED UPDATE SET
-&lt;every column except deal_id, first_seen_run, day1_hot_score, day1_hot_flag&gt; WHEN NOT MATCHED INSERT ROW — inside BEGIN/COMMIT
-TRANSACTION with the audit and state statements.</t>
+          <t>Pass 3 phase 2 — sql/new_deals_batch.sql (PROCEDURE new_deals_batch, called by sql/new_deals_weekly.sql): CREATE OR REPLACE TEMP TABLE
+batch AS SELECT * FROM new_deals_batch_rows(…); MERGE `new_deals` t USING batch s ON t.deal_id = s.deal_id WHEN MATCHED AND
+s.last_seen_run &gt;= IFNULL(t.last_seen_run, …) THEN UPDATE SET &lt;every column except deal_id, first_seen_run, day1_hot_score,
+day1_hot_flag&gt; WHEN NOT MATCHED THEN INSERT ROW — inside BEGIN/COMMIT TRANSACTION with the audit and state statements; mode dry
+writes one runs row and nothing else; any error → ROLLBACK, FAILED runs row, RAISE.</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1397,8 +1403,10 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>sql/new_deals_weekly.sql: MERGE report_state for report_id = CONCAT('NEW_DEALS_', entity, '_C'), watermark = run_ts, in the SAME
-transaction as the new_deals MERGE — the engine enforces "advance only after a successful MERGE".</t>
+          <t>Pass 3 phase 2 — new_deals_batch with advance_state = TRUE and state_report_id = CONCAT('NEW_DEALS_', entity, '_C'): MERGE
+report_state with watermark = GREATEST(old, run_ts) (a replayed run_time never rewinds) in the SAME transaction as the new_deals MERGE —
+the engine enforces "advance only after a successful MERGE"; before the transaction the procedure RAISEs if A's lock_until for the
+entity is live (a fallback run never collides with a live lane-A run).</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1683,7 +1691,9 @@
 OK | ERROR | DRY, http_status, error, dry_run); plus `bq ls --transfer_run` history. DDL: cloud_function_new_deals/bigquery_schema.sql
 (new_deals_runs, new_deals_history) + sql/audit_tables.sql (writeback_log). Pass 3 phase 1: data_gaps on the runs row (sync_stale on
 the ABORTED row; source_detail_unavailable; raw_backfilled_from_current_sync when run_time is older than an hour) and the deals_raw /
-labels_raw slices from sql/land_raw.sql, kept even when the transaction fails. DDL for both raw tables: bigquery_schema.sql.</t>
+labels_raw slices from sql/land_raw.sql, kept even when the transaction fails. DDL for both raw tables: bigquery_schema.sql. Phase 2:
+the procedure writes the runs row (OK, FAILED with @@error.message, or dry_run = TRUE) and the history slice; the script adds
+raw_landing_failed / raw_slice_replaced / labels_missing from its landing, the procedure labels_missing / dedup_horizon_partial.</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -4621,7 +4631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4901,6 +4911,33 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>pass 3 phase 2 — before registering the new lane-C script (dev dataset, credentials)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>the 15 golden vectors through the root → deals_landed_v1 → new_deals_batch_rows vs their expected score and flag; one lane-C run_ts through deals_landed_v1 vs deals_synced_v1</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>n/a until phase 3 (lane A still shapes in Python; tests/test_hot_score.py pins main.hot_score to the same vectors)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>C: sql/apply.sh against DATASET=hubspot_dev, then bq query --use_legacy_sql=false &lt; &lt;(sed "s/\${PROJECT}/$PROJECT/g; s/\${DATASET}/hubspot_dev/g" tests/pass3_batch_vectors.sql); after one transfer run at run_ts X: SELECT COUNT(*) FROM deals_landed_v1 l FULL JOIN deals_synced_v1 s USING (deal_id) WHERE l.run_ts = X AND l.orchestrator = 'bigquery-scheduled-query' AND (s.deal_id IS NULL OR l.dealname != s.dealname OR l.stage_probability != s.stage_probability OR l.amount != s.amount)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>every vectors row ok = TRUE (15 rows; the slice is dropped by the script); the landed/synced comparison returns 0 for deals created in the 90-day window as of X</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Chain of clocks: DTS transfer every day 02:00 UTC → scheduled queries new-deals-&lt;entity&gt;-C "every monday 04:00" (UTC only) →
+          <t>Chain of clocks: DTS transfer every day 02:00 UTC → scheduled queries new-deals-&lt;entity&gt;-C "every monday 03:53" / "04:23" (per entity, off the hour, UTC only) →
 Cloud Scheduler new-deals-writeback 30 5 * * 1 Europe/Zurich POSTing jobs.run with --oauth-service-account-email new-deals-scheduler@.
 Gates: DISABLE_SCHEDULE=1 registers without auto-scheduling (manual `bq mk --transfer_run`); WRITEBACK_APPROVE unset → DRY rows only.</t>
         </is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>sql/sync_transfer.sh: DTS "every day 02:00" (UTC) → sql/scheduled_query.sh: "every monday 04:00" (UTC only, DST-insensitive) →
+          <t>sql/sync_transfer.sh: DTS "every day 02:00" (UTC) → sql/scheduled_query.sh: "every monday 03:53" (SEALSQ) / "04:23" (ICALPS) — per entity and off the hour (two scripts in one minute would be cancelled as conflicting transactions; an on-the-hour schedule can trigger twice), UTC only, DST-insensitive →
 writeback/deploy_job.sh: Cloud Scheduler new-deals-writeback "30 5 * * 1" Europe/Zurich POST jobs.run with --oauth-service-account-email
 new-deals-scheduler@, 3 retries (start failures only). Not paused on create; harmless while WRITEBACK_APPROVE=0.</t>
         </is>
@@ -1118,7 +1118,7 @@
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Same result when A and B2 read the same SCHEDULE_* values from .env (they do) and C's chain keeps its slack (sync 02:00 UTC &lt; query
-04:00 UTC &lt; write-back 05:30 Zurich &lt; A's 07:00 Zurich). C's scheduled query drifts one hour across DST relative to the Zurich jobs
+03:53 / 04:23 UTC &lt; write-back 05:30 Zurich &lt; A's 07:00 Zurich). C's scheduled query drifts one hour across DST relative to the Zurich jobs
 (C-G3); Scheduler retries re-run the same half-open window in A/B2 but only re-issue jobs.run in C (C-G9).</t>
         </is>
       </c>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Chain with slack (transfer 02:00 UTC, query Mon 04:00 UTC), lookback_days = 14 ≥ 2× cadence, freshness guard in sql/new_deals_weekly.sql (RAISE + ABORTED run row when MAX(lastmodified) &lt; run_ts − 36 h); accept one-cycle lag or keep A's extractor.</t>
+          <t>Chain with slack (transfer 02:00 UTC, queries Mon 03:53 / 04:23 UTC), lookback_days = 14 ≥ 2× cadence, freshness guard in sql/new_deals_weekly.sql (RAISE + ABORTED run row when MAX(lastmodified) &lt; run_ts − 36 h); accept one-cycle lag or keep A's extractor.</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>SCHEDULE_UTC="every monday 04:00" chosen so it is always before the 05:30-Zurich write-back and A's 07:00; alternative: drive the SQL from the Zurich-scheduled job.</t>
+          <t>SCHEDULE_UTC_SEALSQ="every monday 03:53" / SCHEDULE_UTC_ICALPS="every monday 04:23" (per entity, off the hour — pass 3 phase 2 review) chosen so both are always before the 05:30-Zurich write-back and A's 07:00; alternative: drive the SQL from the Zurich-scheduled job.</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">

--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="210" customHeight="1">
+    <row r="2" ht="240" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Verdict (pre-flight, 2026-10-05, commit 9e7e18a and the critic fixes that followed — no scenario has yet run against GCP): the three scenarios are built to converge on
@@ -533,11 +533,12 @@
 Divergent by mechanism (deploy unit, identity, secrets, extraction source, delivery, write-back, access, concurrency, observability,
 cost) and each names the file that makes them equivalent. Pass 0 (scaffold): commits 15c926b scoring, b5c37ab + c6a7cc9 scenario A,
 913f63a scenario C, 9e7e18a scenario B; offline evidence tests/test_hot_score.py (15 vectors, JS == Python), tests/test_main_offline.py
-(6 tests), tests/test_n8n_code.py (Code node == main.shape()), DRYRUN=1 rehearsals of deploy.sh, sql/apply.sh, deploy/n8n/*.sh,
+(6 tests), tests/test_n8n_code.py (Code node == main.shape(); retired with B2 in pass 3 phase 3), DRYRUN=1 rehearsals of deploy.sh, sql/apply.sh, deploy/n8n/*.sh,
 writeback/deploy_job.sh. The probe for pass 1 is `deploy.sh probe` / `deploy.sh status` (bq over new_deals, new_deals_runs,
 report_state) — paste its dated output here after the first live run. Recommendation: A as the production orchestrator with B1
 (workflows/NEW_DEALS_DELIVERY.json) as its delivery tail and C's compute views + write-back job as the Breeze-facing extension; B2 only if
-the n8n editor must be the operating surface.</t>
+the n8n editor must be the operating surface. 2026-10-21 (pass 3 phase 3): B2 retired (D6); L5/L6/L7/L13 are one implementation,
+sql/new_deals_batch.sql over the raw root, that every lane CALLs.</t>
         </is>
       </c>
     </row>
@@ -596,19 +597,18 @@
         <is>
           <t>Cloud Scheduler HTTP jobs new-deals-SEALSQ (0 7 * * 1) and new-deals-ICALPS (20 7 * * 1) Europe/Zurich, OIDC as the SA with
 audience = service URL, --attempt-deadline 600s, 3 retries, created PAUSED and resumed by `deploy.sh enable` after `deploy.sh dry`;
-manual: curl with `gcloud auth print-identity-token`; ?dry_run=1 reads everything, writes nothing.</t>
+manual: curl with `gcloud auth print-identity-token`; ?dry_run=1 lands with mode dry and leaves one runs row (D1), nothing in the sink or the state.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>hubspot.report_state (watermark + lock_until lease per NEW_DEALS_&lt;entity&gt;), hubspot.new_deals (MERGE on deal_id), per-run staging
-new_deals_staging_&lt;entity&gt;_&lt;run_ts&gt; (dropped), hubspot.new_deals_runs + new_deals_history (audit), Secret Manager hubspot-token:&lt;pinned&gt;,
+          <t>hubspot.report_state (watermark + lock_until lease per NEW_DEALS_&lt;entity&gt;), hubspot.new_deals (MERGE on deal_id), hubspot.new_deals_runs + new_deals_history (audit), Secret Manager hubspot-token:&lt;pinned&gt;,
 .env (gitignored) for PROJECT/REGION/DATASET.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Fully programmed; offline tests prove dry-reads/no-writes, per-run staging, frozen update list, watermark after MERGE, 409 on an
+          <t>Fully programmed; offline tests prove the dry gate (D1), land → CALL new_deals_batch → watermark, the CALL contract, both failure paths, 409 on an
 overlapping lease, event mode never touching the watermark. First-deploy expectation medium: one or two IAM / API iterations, and
 new_deals_history must exist before the first live run (R44). Cheapest (&lt; $1/month) and the only keyless lane.</t>
         </is>
@@ -622,7 +622,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>deploy/n8n/{secrets.sh, cloudsql.sh, deploy_n8n.sh, import_workflows.sh, scheduler.sh}; service.yaml applied with
+          <t>deploy/n8n/{secrets.sh, cloudsql.sh, deploy_n8n.sh, import_workflows.sh} (scheduler.sh retired with B2); service.yaml applied with
 `gcloud run services replace` (pinned image docker.io/n8nio/n8n:2.41.7); workflows/*.json generated by workflows/src/build_workflow.py
 (stable ids → re-import updates in place) and imported through the public REST API with X-N8N-API-KEY.</t>
         </is>
@@ -832,7 +832,7 @@
 to compare between two scenarios after each stage. Source: the CloudBQ repository on branch claude/cloud-run-bigquery-pipeline-e94ziy
 at 2026-10-05 (9e7e18a): cloud_function_new_deals/{main.py, deploy.sh, bigquery_schema.sql}, scoring/, sql/, writeback/, deploy/n8n/,
 workflows/, tests/; scratchpad/discovery/scenario_{A,B,C}.md and result_{A,B,C}.json; the user's scenario notes and risk table of
-2026-10-05. Nothing has run against GCP: every "not yet" is the first authenticated run's job. Parity here is OUTCOME parity: Parallel means the same tables, keys, constants and audit rows whichever lane runs, proven by tests/ (Python == JS) and by the equality checks once credentials exist; L5/L7/L8/L13 are three code paths that must agree, not one shared code path.</t>
+2026-10-05. Nothing has run against GCP: every "not yet" is the first authenticated run's job. Parity here is OUTCOME parity: Parallel means the same tables, keys, constants and audit rows whichever lane runs, proven by tests/ (Python oracle == SQL UDF; since pass 3 one SQL implementation) and by the equality checks once credentials exist; L5/L7/L8/L13 were three code paths that had to agree — since pass 3 phase 3 L5/L6/L7/L13 are one shared SQL path.</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>B · n8n on Cloud Run (B1 delivery tail NEW_DEALS_DELIVERY.json; B2 full pipeline NEW_DEALS_FULL.json via Scheduler → webhook)</t>
+          <t>B · n8n on Cloud Run (B1 delivery tail NEW_DEALS_DELIVERY.json; B2 — n8n owning the pipeline, NEW_DEALS_FULL.json — retired in pass 3 phase 3, decision D6; its cells record the design as built)</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -959,7 +959,7 @@
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Every unit is a create-or-update script reading the same .env (.env.example) and honouring DRYRUN=1; workflows are generated, never
-hand-edited (build_workflow.py --check in tests/test_n8n_code.py); docs/diffs ledger keeps one patch per commit.</t>
+hand-edited (build_workflow.py --check in CI); docs/diffs ledger keeps one patch per commit.</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>B1: n8n never touches BigQuery. B2: Google Service Account credential = exported JSON key of n8n-bq@ written by deploy/n8n/secrets.sh
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B1: n8n never touches BigQuery. B2: Google Service Account credential = exported JSON key of n8n-bq@ written by deploy/n8n/secrets.sh
 to deploy/n8n/.secrets/n8n-bq.key.json (gitignored), same jobUser + DCL GRANT; stored encrypted in Cloud SQL under N8N_ENCRYPTION_KEY.
 n8n has no ADC / Workload Identity path. Runtime SA n8n-run@ holds only cloudsql.client + secretAccessor.</t>
         </is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>B1: A's jobs; the function then POSTs to the webhook. B2: deploy/n8n/scheduler.sh — jobs n8n-new-deals-SEALSQ / -ICALPS with the same
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B1: A's jobs; the function then POSTs to the webhook. B2: deploy/n8n/scheduler.sh — jobs n8n-new-deals-SEALSQ / -ICALPS with the same
 SCHEDULE_SEALSQ / SCHEDULE_ICALPS and time zone from .env, POST $N8N_URL/webhook/new-deals-run?entity=…, header X-Delivery-Token from
 secret n8n-webhook-token, --attempt-deadline 900s, 3 retries, created PAUSED; `scheduler.sh enable` resumes. (In-app Schedule Trigger
 is not used: it never fires at minScale 0, B-G01.)</t>
@@ -1150,14 +1150,15 @@
         <is>
           <t>main.py read_watermark(): SELECT watermark FROM report_state WHERE report_id = 'NEW_DEALS_&lt;entity&gt;' (default now − FIRST_RUN_DAYS=7);
 HubSpot POST /crm/v3/objects/deals/search createdate GTE watermark − OVERLAP_MINUTES(5) AND LT run_ts, PROPS (29 properties), sort
-createdate ASC, 200/page; deals filtered by ENTITIES[entity].pipelines, the rest kept as duplicate candidates ("others"). Pass 3
-phase 1: the whole search result (in_scope per deal) and the pipeline/stage/owner maps land in deals_raw / labels_raw keyed by
-(run_ts, entity, orchestrator) before shape() — load first, delete-older second; non-fatal (data_gaps raw_landing_failed); dry does not land.</t>
+createdate ASC, 200/page; deals filtered by ENTITIES[entity].pipelines, the rest kept as duplicate candidates ("others"). Pass 3:
+the whole search result (in_scope per deal) and the pipeline/stage/owner maps land in deals_raw / labels_raw keyed by (run_ts,
+entity, orchestrator) — load first, delete-older second, time-boxed; since phase 3 a landing failure fails the run (named
+raw_landing_failed) and dry runs land too, with mode = dry (D1). The function computes nothing from the search itself.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>B1: in the function. B2: node "Read watermark" (same SELECT, same report_id) → Code node "Window" computes watermark_in / query_start /
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B1: in the function. B2: node "Read watermark" (same SELECT, same report_id) → Code node "Window" computes watermark_in / query_start /
 query_end once → HTTP Request "HubSpot search" with the identical filterGroups, PROPS list, sort and limit 200, paginated on
 paging.next.after; "Pipelines" and "Owners" HTTP nodes for labels.</t>
         </is>
@@ -1194,7 +1195,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>A: tests/test_main_offline.py::test_dry_reads_but_writes_nothing (watermark read in dry mode) and test_first_run_without_watermark_uses_first_run_days;
+          <t>A: tests/test_main_offline.py::test_dry_lands_calls_with_mode_dry_and_touches_no_sink_or_state (watermark read in dry mode) and test_first_run_without_watermark_uses_first_run_days;
 B2: tests/test_n8n_code.py (Window values flow into the payload). C: by reading sql/new_deals_weekly.sql; synced columns unknown until
 the first transfer run (R36). Live search: not yet — first authenticated run.</t>
         </is>
@@ -1213,13 +1214,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>main.py hot_score() — W, BIAS = −6.4788, THRESHOLD = 45.0, CR {12096408: 84/730, 13772279: 51/303}, MAXC = 223; round(s, 1);
-(None, None) for other pipelines. Canonical: tests/test_hot_score.py rebuilds tests/hot_score_vectors.json from it.</t>
+          <t>Pass 3 phase 3: the function no longer scores — CALL new_deals_batch runs new_deals_batch_rows, which applies the persistent UDF hot_score_v1 (scoring/hot_score_v1.sql) with run_ts as "now"; main.py hot_score() survives as the test oracle that builds tests/hot_score_vectors.json (tests/test_hot_score.py) and tests/pass3_batch_vectors.sql proves the UDF on the same vectors through the root.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>workflows/src/shape_score.js hotScore() injected into the Code node "Shape + score" with the constants from
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] workflows/src/shape_score.js hotScore() injected into the Code node "Shape + score" with the constants from
 scoring/hot_score_v1.constants.json at build time (build_workflow.py code_js()); scoring/hot_score_v1.mjs is the standalone JS port
 used by the write-back job and run by the test.</t>
         </is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Nothing by design: one constants file, one vector file, three ports. The only tolerated difference is a 0.1 step at an exact
+          <t>Nothing by design: one constants file, one vector file, one UDF since pass 3 (Python is the test oracle; the JS port retired with B2). The only tolerated difference is a 0.1 step at an exact
 rounding tie (Python half-to-even vs JS/SQL half-away), asserted as |Δscore| ≤ 0.1 with raw |Δ| &lt; 1e-9 (B-G11, contested: unreachable
 in practice).</t>
         </is>
@@ -1253,7 +1253,7 @@
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>tests/test_hot_score.py 2026-10-05: 15 vectors, "constants OK · python vectors OK · JS port OK (raw |Δ| &lt; 1e-9, flags equal)";
-tests/test_n8n_code.py row-for-row equality incl. day1_hot_score; SQL UDF: DuckDB harness offline 0/4,000 mismatches
+(B2 retired) tests/test_n8n_code.py row-for-row equality incl. day1_hot_score; SQL UDF: DuckDB harness offline 0/4,000 mismatches, tests/pass3_batch_vectors.sql through the root
 (scenario_C.md) — `bq query &lt; tests/hot_score_vectors.sql` (every ok = TRUE): not yet — first authenticated run.</t>
         </is>
       </c>
@@ -1271,14 +1271,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>main.py name_key() (final_customer else first token of dealname split on -/|(, lower-cased alphanumerics, 40 chars) and shape():
-31 columns = bigquery_schema.sql; dup_in_batch across all pipelines in the window; dup_known from recent_names() (new_deals, 90 days,
-every entity, key → [deal_ids], self excluded, ERROR log + empty map on failure); rows sorted (−amount_kusd, deal_id).</t>
+          <t>Pass 3 phase 3: shaping and the duplicate flag happen in the table function new_deals_batch_rows (sql/deals_landed_v1.sql) over the slice the function landed — name_key in the view, labels from labels_raw, duplicates = lane C's rule over the root (D3); main.py shape() / name_key() survive as test oracles (tests/test_main_offline.py renders the fake history slice from them).</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>workflows/src/shape_score.js nameKey() / shapeRows() — same regexes, same batch + known logic; node "Recent names" runs the same
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] workflows/src/shape_score.js nameKey() / shapeRows() — same regexes, same batch + known logic; node "Recent names" runs the same
 90-day SELECT with continue-on-fail (→ empty map like A); same sort. Column list comes from bigquery_schema.sql at build time.</t>
         </is>
       </c>
@@ -1298,9 +1296,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Same flag when the twin is in the same window or already in hubspot.new_deals within 90 days. C sees every twin in the synced table,
-including deals A never reported (older than A's first run) — C is the stricter rule (C-G5); duplicate_of ordering differs
-(A: batch then known; C: by createdate).</t>
+          <t>None since pass 3 phase 3: one rule over the root for every lane (sql/deals_landed_v1.sql, decision D3); the only residue is the horizon until the root is 90 days old (dedup_horizon_partial on the runs row).</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1311,7 +1307,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>A == B2: tests/test_n8n_code.py::test_code_node_matches_python_shape (every field of every row, dup twin in batch + warehouse);
+          <t>A: tests/test_main_offline.py::test_row_contract_equals_schema; one implementation for every lane since pass 3, proved by tests/test_pass3_sql.py and tests/pass3_batch_vectors.sql (B2 retired; its former proof tests/test_n8n_code.py::test_code_node_matches_python_shape covered every field of every row, dup twin in batch + warehouse);
 A: tests/test_main_offline.py::test_row_contract_equals_schema (31 columns). C: by reading the SQL; not yet — first authenticated run.</t>
         </is>
       </c>
@@ -1329,14 +1325,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>main.py merge_rows(): load_table_from_json into per-run staging new_deals_staging_&lt;entity&gt;_&lt;run_ts&gt; (WRITE_TRUNCATE, schema of
-new_deals), then MERGE `new_deals` t USING staging s ON t.deal_id = s.deal_id WHEN MATCHED UPDATE SET every column except FROZEN =
-(deal_id, first_seen_run, day1_hot_score, day1_hot_flag) WHEN NOT MATCHED INSERT; staging dropped in finally.</t>
+          <t>Pass 3 phase 3: ONE statement — CALL `$PROJECT.$DATASET.new_deals_batch`(@run_ts, @entity, 'cloud-run-function', @mode, FALSE, NULL, @watermark_in, @query_start, @query_end, @started_ms, @gaps) — the procedure MERGEs new_deals from the table function (frozen four untouched, older-slice guard), writes the history slice and the runs row in one transaction; no per-run staging table any more; CALL_TIMEOUT_S (300 s).</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>B2 node "MERGE new_deals": one Execute Query whose USING source is SELECT … FROM UNNEST(JSON_QUERY_ARRAY(PARSE_JSON('''&lt;rows json&gt;'''))) r
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B2 node "MERGE new_deals": one Execute Query whose USING source is SELECT … FROM UNNEST(JSON_QUERY_ARRAY(PARSE_JSON('''&lt;rows json&gt;'''))) r
 with SAFE_CASTs per column type; same ON deal_id, same frozen set — generated by build_workflow.py sql_templates() from
 bigquery_schema.sql. No staging table, no streaming insert (B-G08/B-G09).</t>
         </is>
@@ -1357,7 +1351,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Same target, same key, same update list, same insert; only the MERGE's source differs (per-run staging table / inline JSON / TEMP
+          <t>Same target, same key, same update list, same insert — since pass 3 one source too: the procedure's TEMP table for A and C (B2 retired). Before: (per-run staging table / inline JSON / TEMP
 table) and none of those sources is shared or persistent, so nothing local can change the outcome. Re-running a window writes nothing
 new on any surface.</t>
         </is>
@@ -1370,7 +1364,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>A: tests/test_main_offline.py::test_live_uses_per_run_staging_and_frozen_update_list (one staging table, dropped; day1_* and
+          <t>A: tests/test_main_offline.py::test_live_lands_before_the_call_and_advances_the_watermark_after_it (no staging table; the frozen set is proved by tests/test_pass3_sql.py::test_merge_update_list_excludes_the_frozen_columns; day1_* and
 first_seen_run absent from UPDATE SET); B2: tests/test_n8n_code.py asserts JSON_QUERY_ARRAY source and no day1_hot_score in the
 UPDATE list; C: the UPDATE list read against the schema (27 columns, same exclusions). MERGE executed: not yet — first authenticated run.</t>
         </is>
@@ -1389,14 +1383,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>main.py write_watermark(): UPDATE report_state SET watermark = run_ts, updated_at = CURRENT_TIMESTAMP(), lock_until = NULL WHERE
-report_id = 'NEW_DEALS_&lt;entity&gt;' — called only after merge_rows() and write_history() succeeded, window mode only (event mode and
-dry mode never touch it); the row is created on first run by acquire_lease().</t>
+          <t>main.py write_watermark(): UPDATE report_state SET watermark = run_ts, updated_at = now, lock_until = NULL WHERE report_id = 'NEW_DEALS_&lt;entity&gt;' — after a successful CALL and the read-back of the rows (the procedure is called with advance_state = FALSE: the lease and A's row stay in the function; a read-back failure keeps the window replayable); never in event or dry mode; tests/test_main_offline.py pins the order land → CALL → read → watermark.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>B2 node "Advance watermark": MERGE report_state USING (SELECT 'NEW_DEALS_&lt;entity&gt;', TIMESTAMP '&lt;run_ts&gt;') … UPDATE SET watermark,
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B2 node "Advance watermark": MERGE report_state USING (SELECT 'NEW_DEALS_&lt;entity&gt;', TIMESTAMP '&lt;run_ts&gt;') … UPDATE SET watermark,
 updated_at, lock_until = NULL / INSERT — wired strictly after "MERGE new_deals" and "History slice" with the default On Error = stop,
 skipped entirely on the dry branch.</t>
         </is>
@@ -1429,8 +1421,8 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>A: tests/test_main_offline.py::test_live_uses_per_run_staging_and_frozen_update_list (MERGE index &lt; watermark index, lease released)
-and ::test_event_mode_never_touches_watermark; B2: tests/test_n8n_code.py asserts the watermark MERGE text and report_id; C: by reading
+          <t>A: tests/test_main_offline.py::test_live_lands_before_the_call_and_advances_the_watermark_after_it (CALL index &lt; watermark index, lease released)
+and ::test_event_mode_calls_with_mode_event_and_never_touches_state; B2: tests/test_n8n_code.py asserts the watermark MERGE text and report_id; C: by reading
 the transaction. report_state rows: not yet — first authenticated run.</t>
         </is>
       </c>
@@ -1454,7 +1446,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>B1 workflows/NEW_DEALS_DELIVERY.json: Webhook new-deals (Header Auth, respond lastNode) → IF Any rows? → Split Out rows → Code
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B1 workflows/NEW_DEALS_DELIVERY.json: Webhook new-deals (Header Auth, respond lastNode) → IF Any rows? → Split Out rows → Code
 "Shape columns" → Convert to File XLSX → Email Send (MAIL_FROM/MAIL_TO from env); false branch "Email (no rows)". B2: the same tail
 inside NEW_DEALS_FULL after "Run log" (XLSX NEW_DEALS_&lt;entity&gt;_&lt;date&gt;.xlsx, text body with [DUP]/[HOT] markers).</t>
         </is>
@@ -1509,7 +1501,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Not generated: B2 could add a HubSpot Deal → Update node or an HTTP Request to /crm/v3/objects/deals/batch/update behind the same
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] Not generated: B2 could add a HubSpot Deal → Update node or an HTTP Request to /crm/v3/objects/deals/batch/update behind the same
 skip rule; it would need the write token inside n8n. Not in v1.</t>
         </is>
       </c>
@@ -1560,12 +1552,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>`deploy.sh dry`: ?dry_run=1 for both entities; main.py builds the BigQuery client in dry mode, reads watermark + warehouse twins, skips MERGE, history, watermark, run row and delivery; payload carries dry_run: true; the step asserts rows_written == 0 and prints rows/dup/hot/window. curl -sSf: an HTTP 403 (caller lacks run.invoker) or 409 (lease held) fails the gate instead of passing a JSON error as a payload (R50). Nothing is written; the lease is not taken. Same gate from the Workbench notebook (cells 3.8 and 4.6) and the Cloud Shell runbook Phase 7.</t>
+          <t>`deploy.sh dry`: ?dry_run=1 for both entities; since pass 3 phase 3 (D1) a dry run lands its slice with mode = dry and CALLs the procedure with mode = dry — one new_deals_runs row (dry_run TRUE, rows_written 0), no MERGE, no history, no state, no lease, no delivery; the payload comes from new_deals_batch_rows; the step still asserts rows_written == 0 and prints rows/dup/hot/window; curl -sSf: an HTTP 403 or 409 fails the gate (R50).</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>B2: POST /webhook/new-deals-run?entity=…&amp;dry_run=1 → IF "Dry run?" true → "Respond" with the payload (rows_written 0, dry_run true);
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B2: POST /webhook/new-deals-run?entity=…&amp;dry_run=1 → IF "Dry run?" true → "Respond" with the payload (rows_written 0, dry_run true);
 the BigQuery reads still run, the write nodes and the email do not. Manual execution in the editor (pinned data) is the
 n8n-native rehearsal; Scheduler jobs stay PAUSED until the gate passes.</t>
         </is>
@@ -1597,7 +1589,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>A: tests/test_main_offline.py::test_dry_reads_but_writes_nothing; B2: tests/test_n8n_code.py (dry_run true, rows_written 0) and the IF
+          <t>A: tests/test_main_offline.py::test_dry_lands_calls_with_mode_dry_and_touches_no_sink_or_state; B2 (retired): tests/test_n8n_code.py (dry_run true, rows_written 0) and the IF
 wiring in NEW_DEALS_FULL.json; C: DRYRUN=1 sql/scheduled_query.sh renders (bq --dry_run itself needs credentials: not yet — first
 authenticated run).</t>
         </is>
@@ -1621,7 +1613,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>B2: the same UPDATE on report_state (bq query), then POST the webhook without dry_run (or `gcloud scheduler jobs run
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B2: the same UPDATE on report_state (bq query), then POST the webhook without dry_run (or `gcloud scheduler jobs run
 n8n-new-deals-&lt;entity&gt;`); identical MERGE / frozen set / history DELETE+INSERT by (run_ts, entity, orchestrator = 'n8n').</t>
         </is>
       </c>
@@ -1670,16 +1662,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>main.py write_run(): one row per run in hubspot.new_deals_runs (run_ts, entity, mode, dry_run, orchestrator = 'cloud-run-function',
-window, row_count, rows_written, duplicate_suspects, day1_hot, status OK | OK_DELIVERY_FAILED | FAILED, error, duration_ms) — also in
-the exception path; write_history(): the run's rows appended to hubspot.new_deals_history (slice replaced by run_ts/entity/orchestrator);
-JSON log line "run complete". Pass 3 phase 1: new_deals_runs.data_gaps ARRAY&lt;STRING&gt; names what the run could not read or compute
-(raw_landing_failed, dedup_scope_batch_only, event_no_window); deals_raw / labels_raw hold the run's inputs as delivered (JSON).</t>
+          <t>Pass 3 phase 3: the procedure writes the runs row (status OK, or FAILED with the message before re-raising; dry_run TRUE for a dry run) and the history slice inside its transaction; the function writes the FAILED row itself only when no row exists after a failure (search, landing, a CALL that never reached the procedure), amends the procedure's OK row to FAILED when it fails after the CALL, and to OK_DELIVERY_FAILED when the delivery tail fails; the payload's rows_written and data_gaps are read from that row; data_gaps from the function (event_no_window, raw_slice_replaced, raw_landing_failed) plus the procedure's (labels_missing, dedup_horizon_partial); deals_raw / labels_raw hold the run's inputs; JSON log line "run complete".</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>B2 nodes "History slice" (DELETE + INSERT new_deals_history … orchestrator = 'n8n') and "Run log" (INSERT new_deals_runs … 'n8n',
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B2 nodes "History slice" (DELETE + INSERT new_deals_history … orchestrator = 'n8n') and "Run log" (INSERT new_deals_runs … 'n8n',
 status 'OK'); n8n execution records in Cloud SQL (90 days, EXECUTIONS_DATA_MAX_AGE=2160) and NEW_DEALS_ERRORS.json e-mails failures.
 B1: new_deals_runs.status from the function records the delivery outcome.</t>
         </is>
@@ -1790,14 +1778,14 @@
       <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Data model first: report_state.lock_until lease taken by one atomic UPDATE (num_dml_affected_rows == 1, LEASE_MINUTES=12; an
-overlapping run gets 409 and writes nothing), per-run staging table, MERGE on deal_id, watermark after MERGE. Runtime second:
+overlapping run gets 409 and writes nothing), land → CALL new_deals_batch (MERGE on deal_id in one transaction) → watermark after the CALL. Runtime second:
 --max-instances 1 --concurrency 1, --timeout 540 &lt; --attempt-deadline 600s, 3 retries, schedules offset 07:00 / 07:20 so the two
 entities never share a minute.</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>B2: N8N_CONCURRENCY_PRODUCTION_LIMIT=1 + maxScale 1 serialise executions; Webhook responseMode responseNode (responds when done) with
+          <t>[B2 retired in pass 3 phase 3 (D6): the text records the design as built; only B1 remains] B2: N8N_CONCURRENCY_PRODUCTION_LIMIT=1 + maxScale 1 serialise executions; Webhook responseMode responseNode (responds when done) with
 timeoutSeconds 900 ≥ attempt-deadline 900s so Scheduler retries only on real failure; cpu-throttling false; Error Workflow. No lease
 row is acquired (the watermark MERGE only clears lock_until). B1: A's guards; the delivery tail is at-least-once.</t>
         </is>
@@ -1989,7 +1977,7 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>B · n8n on Cloud Run (B1 delivery tail NEW_DEALS_DELIVERY.json; B2 full pipeline NEW_DEALS_FULL.json via Scheduler → webhook) — command</t>
+          <t>B · n8n on Cloud Run (B1 delivery tail NEW_DEALS_DELIVERY.json; B2 — n8n owning the pipeline, NEW_DEALS_FULL.json — retired in pass 3 phase 3, decision D6; its cells record the design as built) — command</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
@@ -2030,7 +2018,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>same .env; deploy/n8n/deploy_n8n.sh refuses an unset PROJECT and N8N_IMAGE=:latest; scheduler.sh / secrets.sh / cloudsql.sh require PROJECT</t>
+          <t>same .env; deploy/n8n/deploy_n8n.sh refuses an unset PROJECT and N8N_IMAGE=:latest; secrets.sh / cloudsql.sh require PROJECT (scheduler.sh retired with B2)</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -2148,12 +2136,12 @@
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>deploy.sh tables — renders bigquery_schema.sql (CREATE SCHEMA, report_state + lock_until, new_deals, new_deals_runs, new_deals_last_7d) then GRANT dataEditor</t>
+          <t>deploy.sh tables — renders bigquery_schema.sql (CREATE SCHEMA, report_state + lock_until, new_deals, new_deals_runs (+data_gaps), new_deals_history, deals_raw, labels_raw, new_deals_last_7d) then GRANT dataEditor; deploy.sh routines — hot_score_v1, deals_landed_v1 + new_deals_batch_rows, new_deals_batch (the objects the function CALLs since pass 3; no SYNC_* needed)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>n/a — B2 writes A's tables (its SQL is generated from bigquery_schema.sql); needs new_deals_history from sql/audit_tables.sql too (R44)</t>
+          <t>n/a — n8n writes no table (B1 only; B2 retired in pass 3 phase 3, D6)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -2280,7 +2268,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>deploy/n8n/scheduler.sh create — jobs n8n-new-deals-SEALSQ / -ICALPS created PAUSED (POST webhook, X-Delivery-Token header, 900s, 3 retries)</t>
+          <t>n/a — B1 has no trigger of its own: the function POSTs to NEW_DEALS_DELIVERY (B2 and deploy/n8n/scheduler.sh retired in pass 3 phase 3, D6)</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -2321,7 +2309,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>curl -X POST -H "X-Delivery-Token: $(gcloud secrets versions access latest --secret n8n-webhook-token)" "$N8N_URL/webhook/new-deals-run?entity=SEALSQ&amp;dry_run=1" (and ICALPS); or a manual execution in the editor</t>
+          <t>n/a — B1 has no dry run of its own; a dry run of the function POSTs nothing (B2 retired in pass 3 phase 3, D6)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2336,12 +2324,12 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>payload {report_id, run_timestamp, orchestrator, dry_run: true, window{watermark_in, query_start, query_end}, row_count, rows_written: 0, duplicate_suspects, day1_hot[], rows[]} (A, B2); bytes processed + DRY rows (C)</t>
+          <t>payload {report_id, run_timestamp, orchestrator, dry_run: true, window{watermark_in, query_start, query_end}, row_count, rows_written: 0, duplicate_suspects, day1_hot[], data_gaps[], rows[]} (A; since pass 3 also one new_deals_runs row with dry_run TRUE); bytes processed + DRY rows (C)</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>THE GATE before any LIVE row below. Same numbers for A and B2 on the same window (Equality checks). C's SQL half has no compute-only mode; its dry run is syntax + the dev dataset.</t>
+          <t>THE GATE before any LIVE row below. A's dry run exercises the whole SQL path (landing, table function, the procedure's dry branch), so a missing routine or a broken view fails here (B2 retired). C's SQL half has no compute-only mode; its dry run is syntax + the dev dataset.</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2354,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>curl -X POST -H "X-Delivery-Token: …" "$N8N_URL/webhook/new-deals-run?entity=SEALSQ" (and ICALPS), or gcloud scheduler jobs run n8n-new-deals-SEALSQ</t>
+          <t>n/a — B1 runs when the function delivers: the live run POSTs the payload to NEW_DEALS_DELIVERY (B2 retired, D6)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2381,12 +2369,12 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>rows_written == row_count; hubspot.new_deals holds the rows; report_state NEW_DEALS_&lt;entity&gt; (A, B2) / NEW_DEALS_&lt;entity&gt;_C (C) watermark == run_timestamp; one new_deals_runs row per run</t>
+          <t>rows_written == row_count; hubspot.new_deals holds the rows; report_state NEW_DEALS_&lt;entity&gt; (A) / NEW_DEALS_&lt;entity&gt;_C (C) watermark == run_timestamp; one new_deals_runs row per run (written by the procedure)</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>First run with no watermark looks back FIRST_RUN_DAYS=7 (A, B2) / 14 days lookback (C). Re-running the same window writes nothing new (MERGE). Requires new_deals_history (R44).</t>
+          <t>First run with no watermark looks back FIRST_RUN_DAYS=7 (A) / 14 days lookback (C). Re-running the same window writes nothing new (MERGE). Requires the routines (deploy.sh routines / sql/apply.sh) — a missing procedure fails the CALL (deploy.sh dry catches it).</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2399,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>deploy/n8n/scheduler.sh enable — resume n8n-new-deals-SEALSQ / -ICALPS; activate the workflows (UI or POST /api/v1/workflows/&lt;id&gt;/activate)</t>
+          <t>activate NEW_DEALS_DELIVERY (UI or POST /api/v1/workflows/&lt;id&gt;/activate); nothing to schedule (B2 and scheduler.sh retired, D6)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -2431,7 +2419,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Only after step 8 passed on both entities and step 9 was probed. Same clock on A and B2 is the L3 condition; C's chain must keep its slack. Do not run A and B2 live on the same report_id at the same time (they share the watermark row).</t>
+          <t>Only after step 8 passed on both entities and step 9 was probed. C's chain must keep its slack (per-entity, off-the-hour schedules); the procedure refuses to advance C's row while A holds the entity's lease.</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2496,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>one report_state row per entity per orchestrator family (A/B2 share NEW_DEALS_&lt;entity&gt;; C has _C); watermark == last successful run_timestamp; lock_until NULL between runs</t>
+          <t>one report_state row per entity per lane (A: NEW_DEALS_&lt;entity&gt;; C: _C); watermark == last successful run_timestamp; lock_until NULL between runs</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -4125,7 +4113,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>A's recent_names reads new_deals (90 days); C self-joins the synced table.</t>
+          <t>A''s recent_names read new_deals (90 days); C self-joined the synced table (both before pass 3).</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4135,7 +4123,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>open — decision recorded in L6; equality check compares flags only for twins present in new_deals</t>
+          <t>closed in pass 3 phase 3 (D3) — one implementation over the root, sql/deals_landed_v1.sql; the equality check now compares A and C on the same rule</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4234,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>open — found by reading main.py:write_history vs bigquery_schema.sql on 2026-10-05; step 4 notes carry the workaround</t>
+          <t>closed — new_deals_history lives in bigquery_schema.sql and deploy.sh tables creates it (write_history itself retired in pass 3 phase 3)</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4308,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>open — by reading build_workflow.py sql_templates() (WATERMARK_SQL clears lock_until, nothing sets it)</t>
+          <t>closed by retirement — B2 and build_workflow.py sql_templates() were removed in pass 3 phase 3 (D6)</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4647,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>B · n8n on Cloud Run (B1 delivery tail NEW_DEALS_DELIVERY.json; B2 full pipeline NEW_DEALS_FULL.json via Scheduler → webhook) / C · BigQuery compute (synced deals, hot_score_v1 UDF, scheduled script) + Node 22 write-back job; Breeze reads, Claude iterates — command</t>
+          <t>B · n8n on Cloud Run (B1 delivery tail NEW_DEALS_DELIVERY.json; B2 — n8n owning the pipeline, NEW_DEALS_FULL.json — retired in pass 3 phase 3, decision D6; its cells record the design as built) / C · BigQuery compute (synced deals, hot_score_v1 UDF, scheduled script) + Node 22 write-back job; Breeze reads, Claude iterates — command</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -4676,7 +4664,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>payload row_count, duplicate_suspects, day1_hot[] and window per entity — A vs B2 on the same watermark row</t>
+          <t>payload row_count, duplicate_suspects, day1_hot[] and window per entity — A (B2 retired, D6) and, for the same run_ts, the table function</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4762,12 +4750,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>python3 tests/test_hot_score.py (rebuilds tests/hot_score_vectors.json from main.py and runs node scoring/hot_score_v1.mjs on them); day1_hot_score of the deal in the payload / table</t>
+          <t>python3 -m pytest tests/test_hot_score.py tests/test_hot_score_sql_duckdb.py (Python oracle == SQL UDF on 15 vectors + 4,000 deals; the JS port retired with B2); day1_hot_score of the deal in the payload / table</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>B2: tests/test_n8n_code.py (Code node rows == main.shape()); C: bq query --use_legacy_sql=false &lt; tests/hot_score_vectors.sql (after sql/apply.sh) and SELECT hot_score_v1 FROM `$PROJECT.hubspot.hot_deals_v1` WHERE deal_id = '&lt;id&gt;'</t>
+          <t>B2 retired (D6); C: bq query --use_legacy_sql=false &lt; tests/hot_score_vectors.sql (after sql/apply.sh) and SELECT hot_score_v1 FROM `$PROJECT.hubspot.hot_deals_v1` WHERE deal_id = '&lt;id&gt;'</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -4826,7 +4814,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>A == B2 exactly (tests/test_n8n_code.py offline); C ⊇ A — any extra C suspect has a twin older than A's first run (R41).</t>
+          <t>A == C on the same rule (one table function, D3); a difference can only come from the slices themselves (R41 closed).</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4895,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>0 missing rows for both orchestrators; 0 NULL pipelines in the JSON; data_gaps [] on a clean lane-A run once new_deals holds name_key rows from the last 90 days ([dedup_scope_batch_only] on the first run of an empty warehouse or when recent_names() failed — main.py `if not known`; [raw_slice_replaced] when the key was re-landed); [source_detail_unavailable] on a clean lane-C run (plus raw_backfilled_from_current_sync when run_time is older than an hour); raw slices with no OK runs row = failed or undelivered runs plus the backfill slices, which have no runs row by design</t>
+          <t>0 missing rows for both orchestrators; 0 NULL pipelines in the JSON; data_gaps [] on a clean lane-A run once the root's oldest deal of the last 90 days is at least 83 days old ([dedup_horizon_partial] until then — also right after the backfill; [labels_missing] when no label landed; [raw_slice_replaced] when the key was re-landed; the procedure's gaps are on the runs row, not in the payload); [source_detail_unavailable] on a clean lane-C run (plus raw_backfilled_from_current_sync when run_time is older than an hour); raw slices with no OK runs row = failed or undelivered runs plus the backfill slices, which have no runs row by design</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4912,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>n/a until phase 3 (lane A still shapes in Python; tests/test_hot_score.py pins main.hot_score to the same vectors)</t>
+          <t>the same table function serves lane A since phase 3 — after deploy.sh dry: SELECT deal_id, day1_hot_score FROM new_deals_batch_rows(&lt;run_ts&gt;, 'SEALSQ', 'cloud-run-function', NULL)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">

--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -735,11 +735,11 @@
         </is>
       </c>
       <c r="B11" s="4">
-        <f>COUNTIF(Layers!$F:$F,"Parallel")</f>
+        <f>COUNTIF(Layers!$G:$G,"Parallel")</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>COUNTIF('Pipeline steps'!$G:$G,"Parallel")</f>
+        <f>COUNTIF('Pipeline steps'!$H:$H,"Parallel")</f>
         <v/>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -755,11 +755,11 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>COUNTIF(Layers!$F:$F,"Conditional")</f>
+        <f>COUNTIF(Layers!$G:$G,"Conditional")</f>
         <v/>
       </c>
       <c r="C12" s="4">
-        <f>COUNTIF('Pipeline steps'!$G:$G,"Conditional")</f>
+        <f>COUNTIF('Pipeline steps'!$H:$H,"Conditional")</f>
         <v/>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -775,11 +775,11 @@
         </is>
       </c>
       <c r="B13" s="4">
-        <f>COUNTIF(Layers!$F:$F,"Divergent")</f>
+        <f>COUNTIF(Layers!$G:$G,"Divergent")</f>
         <v/>
       </c>
       <c r="C13" s="4">
-        <f>COUNTIF('Pipeline steps'!$G:$G,"Divergent")</f>
+        <f>COUNTIF('Pipeline steps'!$H:$H,"Divergent")</f>
         <v/>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -820,11 +820,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr"/>
     </row>
-    <row r="17" ht="180" customHeight="1">
+    <row r="17" ht="210" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Legend: Parity column colours — green Parallel, yellow Conditional, orange Divergent. The columns A/B/C are the three candidate
-SCENARIOS (not three terminals), so the Overview's "Ubuntu" column reads as *runtime*. Layers L0–L17 are the execution layer from code
+SCENARIOS (not three terminals), so the Overview's "Ubuntu" column reads as *runtime*; the fourth column R (pass 3, 2026-10-21) is not a scenario but
+the raw root and the one SQL implementation every scenario CALLs — its cells say how each layer is performed inside BigQuery. Layers L0–L17 are the execution layer from code
 acquisition to cost; Pipeline steps are scenario A's deploy.sh sub-commands in deploy order (check-env … invoker → dry gate → run →
 enable → probe/status → replay) with the equivalent B and C step or "n/a"; LIVE gates mark the rows that write to GCP or HubSpot.
 Remediation R01–R46 = the user's risk table (R01–R05) plus every CONFIRMED gap of the verified discovery (result_A/B/C.json) and the
@@ -851,18 +852,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -893,20 +895,25 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>R · The raw root + the one SQL implementation (deals_raw / labels_raw → deals_landed_v1 → new_deals_batch_rows → new_deals_batch), CALLed by A after its landing and by C after its landing — pass 3 (2026-10-21); not a scenario but what every scenario executes</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>Parity</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Where it diverges</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Remediation</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Verified how</t>
         </is>
@@ -944,25 +951,30 @@
 the sync via sql/sync_transfer.sh (bq mk --transfer_config --data_source=hubspot).</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Four SQL objects in the dataset, created idempotently (CREATE OR REPLACE / IF NOT EXISTS) by `deploy.sh tables` + `deploy.sh routines` (lane A; no SYNC_* needed) and by `sql/apply.sh` (lane C; the same files again): cloud_function_new_deals/bigquery_schema.sql (deals_raw, labels_raw, new_deals_runs.data_gaps), scoring/hot_score_v1.sql, sql/deals_landed_v1.sql, sql/new_deals_batch.sql. No runtime of its own — the deploy unit is the dataset.</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Three deploy units, three versioning stories: a Python directory built by Cloud Build, a container image + workflow JSON stored in
 Cloud SQL, SQL text stored inside transfer configs plus a Node job. Only A and C are fully reproducible from git; B's running state also
 includes credentials created in the UI.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Every unit is a create-or-update script reading the same .env (.env.example) and honouring DRYRUN=1; workflows are generated, never
 hand-edited (build_workflow.py --check in CI); docs/diffs ledger keeps one patch per commit.</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>DRYRUN=1 deploy.sh (all sub-commands print their commands); DRYRUN=1 deploy/n8n/deploy_n8n.sh (renders service.yaml, no placeholder);
 DRYRUN=1 sql/apply.sh (5 files render, 17 DDL statements); DRYRUN=1 writeback/deploy_job.sh; build_workflow --check up to date.
@@ -1002,25 +1014,30 @@
 $SYNC_DATASET under a Google-managed identity. Claude's user ADC: dataViewer on hubspot, dataEditor on hubspot_dev (proposed).</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>The caller's identity: the function SA (new-deals-fn@) and the scheduled-query SA (new-deals-sql@) each hold roles/bigquery.dataEditor on the dataset (routines.get/create included) + jobUser; the procedure and the table function read deals_raw / labels_raw only, so lane A needs no grant on the sync dataset (tests/test_pass3_sql.py::test_procedure_and_function_read_the_root_only).</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>A and C are keyless (ADC); B2 needs a long-lived SA key inside n8n's database (B-G10) — a different mechanism and a different
 rotation story (secrets.sh re-creates the key, the credential is re-imported by id).</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>The same two grants for every identity, issued by deploy.sh tables, deploy/n8n/secrets.sh, sql/scheduled_query.sh and
 writeback/deploy_job.sh (one GRANT statement each, double-quoted principal). If org policy blocks key creation, drop the BigQuery
 node for an HTTP Request to the metadata token endpoint (result_B open question).</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>GRANT text identical in the four scripts (read); DRYRUN=1 prints the bindings. IAM applied: not yet — first authenticated run.</t>
         </is>
@@ -1056,24 +1073,29 @@
 (connector.authentication.oauth.accessToken); the schema-write token is used once by writeback/bootstrap_property.sh and not stored.</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>None. The root is landed by the callers (A with HUBSPOT_TOKEN, C from the sync); the SQL objects hold no secret and call no API.</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>A and C hold one pinned Secret Manager version each; B keeps copies inside n8n (Cloud SQL) and the transfer config keeps a third copy.
 Rotation: A redeploy / C `gcloud run jobs update --update-secrets`; B re-create the credential; DTS `bq update --transfer_config --params`.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Pin versions everywhere (deploy.sh secret_version(), deploy_job.sh); two private apps (read-only for A/B/DTS, crm.objects.deals.write
 only for the job, R35); document the three rotation commands in one runbook row.</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>deploy.sh secret_version() resolves the version NUMBER with value(name.basename()) — value(name) returned projects/…/versions/N and would have been rejected by --set-secrets (R47, fixed 574e954, DRYRUN=1 prints the corrected command); deploy_job.sh refuses a missing version (DRYRUN=1 run); secrets.sh DRYRUN=1 lists the three secrets. Secrets created: not yet — first authenticated run.</t>
         </is>
@@ -1110,25 +1132,30 @@
 new-deals-scheduler@, 3 retries (start failures only). Not paused on create; harmless while WRITEBACK_APPROVE=0.</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>None of its own — one CALL per caller run: the function after its landing (Scheduler Mon 07:00 / 07:20 Zurich, or a webhook event), the scheduled query after its landing (Mon 03:53 / 04:23 UTC). Callers never share a minute: conflicting transactions are cancelled by the engine, and an advance_state caller is refused while A holds the entity's lease.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Same result when A and B2 read the same SCHEDULE_* values from .env (they do) and C's chain keeps its slack (sync 02:00 UTC &lt; query
 03:53 / 04:23 UTC &lt; write-back 05:30 Zurich &lt; A's 07:00 Zurich). C's scheduled query drifts one hour across DST relative to the Zurich jobs
 (C-G3); Scheduler retries re-run the same half-open window in A/B2 but only re-issue jobs.run in C (C-G9).</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>.env SCHEDULE_SEALSQ / SCHEDULE_ICALPS shared by deploy.sh and scheduler.sh; SCHEDULE_UTC and WRITEBACK_SCHEDULE in
 sql/scheduled_query.sh and writeback/deploy_job.sh chosen with slack; or drive the SQL from the Zurich-scheduled job for one clock.</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>DRYRUN=1 deploy.sh invoker and DRYRUN=1 scheduler.sh create print identical cron/time-zone arguments (checked); jobs exist: not yet —
 first authenticated run.</t>
@@ -1175,25 +1202,30 @@
 script has no transaction of its own any more).</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>The landing contract: one slice per (run_ts, entity, orchestrator) in deals_raw (properties JSON as delivered, in_scope, createdate, pipeline_id, mode, source, fetched_at) and labels_raw (kind, id, label) — load first, delete-older second, scoped by mode; written by land_raw()/land_labels() (A, the API) and sql/land_raw.sql (C, the sync table); sql/backfill_raw.sh fills the 90-day horizon once (orchestrator = backfill). The implementation never extracts: a failed landing with no slice → RAISE.</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>A and B2 share the mechanism (watermark row + live createdate search); C reads a scheduled snapshot with a fixed lookback — a deal
 created after the last transfer is missing until the next cycle (C-G2), and C never uses the watermark as its window.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>lookback_days ≥ 2× the transfer cadence (14 d vs daily), the 36 h RAISE guard, chain slack (L3); accept one-cycle lag or keep A's
 search/event mode as the extractor and let C only compute from new_deals. For strict parity C could read new_deals (A's output)
 instead of the sync.</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>A: tests/test_main_offline.py::test_dry_lands_calls_with_mode_dry_and_touches_no_sink_or_state (watermark read in dry mode) and test_first_run_without_watermark_uses_first_run_days;
 B2: tests/test_n8n_code.py (Window values flow into the payload). C: by reading sql/new_deals_weekly.sql; synced columns unknown until
@@ -1232,25 +1264,30 @@
 tests/pass3_batch_vectors.sql runs the same 15 vectors through the root → view → table function in a dev dataset.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>scoring/hot_score_v1.sql, the persistent UDF, applied inside new_deals_batch_rows with run_ts as "now" — the one scoring in the pipeline; tests/hot_score_vectors.sql and tests/pass3_batch_vectors.sql (through the root) are its checks; main.hot_score() is the Python oracle that builds the vectors.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Nothing by design: one constants file, one vector file, one UDF since pass 3 (Python is the test oracle; the JS port retired with B2). The only tolerated difference is a 0.1 step at an exact
 rounding tie (Python half-to-even vs JS/SQL half-away), asserted as |Δscore| ≤ 0.1 with raw |Δ| &lt; 1e-9 (B-G11, contested: unreachable
 in practice).</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>None needed. test_constants_match_json() fails the moment main.py drifts from the constants file; a new fit is v2
 (hot_score_v2 + hot_deals_v2), never an edit of v1.</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>tests/test_hot_score.py 2026-10-05: 15 vectors, "constants OK · python vectors OK · JS port OK (raw |Δ| &lt; 1e-9, flags equal)";
 (B2 retired) tests/test_n8n_code.py row-for-row equality incl. day1_hot_score; SQL UDF: DuckDB harness offline 0/4,000 mismatches, tests/pass3_batch_vectors.sql through the root
@@ -1289,23 +1326,28 @@
 Before phase 2 the weekly script did the same over the synced views.</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Conditional</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>deals_landed_v1 (one typed column per property, name_key once) → new_deals_batch_rows(run_ts, entity, orchestrator, window_start): the window (one row per deal, [window_start, run_ts) when given, the whole slice for an event), labels from the slice's labels_raw (id fallback), duplicates = every deal the root knows as of run_ts (any entity, any orchestrator, in scope or not, 90-day horizon, latest observation per deal_id), STRING_AGG by createdate, deal_id — decision D3, the same rule for every caller.</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>None since pass 3 phase 3: one rule over the root for every lane (sql/deals_landed_v1.sql, decision D3); the only residue is the horizon until the root is 90 days old (dedup_horizon_partial on the runs row).</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>For strict parity restrict C's `recent` CTE to deal_id IN (SELECT deal_id FROM new_deals); otherwise document C as stricter and
 compare flags only for deals whose twins are in new_deals (Equality checks).</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>A: tests/test_main_offline.py::test_row_contract_equals_schema; one implementation for every lane since pass 3, proved by tests/test_pass3_sql.py and tests/pass3_batch_vectors.sql (B2 retired; its former proof tests/test_n8n_code.py::test_code_node_matches_python_shape covered every field of every row, dup twin in batch + warehouse);
 A: tests/test_main_offline.py::test_row_contract_equals_schema (31 columns). C: by reading the SQL; not yet — first authenticated run.</t>
@@ -1344,25 +1386,30 @@
 writes one runs row and nothing else; any error → ROLLBACK, FAILED runs row, RAISE.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>new_deals_batch: CREATE OR REPLACE TEMP TABLE batch AS SELECT * FROM new_deals_batch_rows(…); BEGIN TRANSACTION; MERGE new_deals (the frozen four untouched; WHEN MATCHED AND s.last_seen_run &gt;= t.last_seen_run, so an older slice never overwrites a newer observation; INSERT ROW); rows_written = @@row_count. mode = dry: no MERGE.</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Same target, same key, same update list, same insert — since pass 3 one source too: the procedure's TEMP table for A and C (B2 retired). Before: (per-run staging table / inline JSON / TEMP
 table) and none of those sources is shared or persistent, so nothing local can change the outcome. Re-running a window writes nothing
 new on any surface.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>None needed. Keep the frozen set in one place per surface (main.py FROZEN, build_workflow.py frozen, the UPDATE list in
 new_deals_weekly.sql) and let the Equality check "after a second identical run" prove it.</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>A: tests/test_main_offline.py::test_live_lands_before_the_call_and_advances_the_watermark_after_it (no staging table; the frozen set is proved by tests/test_pass3_sql.py::test_merge_update_list_excludes_the_frozen_columns; day1_* and
 first_seen_run absent from UPDATE SET); B2: tests/test_n8n_code.py asserts JSON_QUERY_ARRAY source and no day1_hot_score in the
@@ -1401,25 +1448,30 @@
 entity is live (a fallback run never collides with a live lane-A run).</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>When advance_state = TRUE (lane C, report_id NEW_DEALS_&lt;entity&gt;_C): MERGE report_state with watermark = GREATEST(old, run_ts) in the same transaction as the new_deals MERGE, after RAISEing if A's lock_until for the entity is live. When FALSE (lane A, events, dry): the procedure touches no state and the caller advances its own row after the CALL and the read-back.</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Same row semantics on every surface: hubspot.report_state.watermark = run_ts of the last successful MERGE, never advanced by a dry run,
 a failed run or an event. C deliberately writes its own key NEW_DEALS_&lt;entity&gt;_C so A's watermark is never overwritten while both are
 deployed (C-G4); the "status" probe therefore shows up to four rows.</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>None needed for the semantics. If C ever becomes the only orchestrator, rename its key to NEW_DEALS_&lt;entity&gt; after pausing A's
 jobs (deploy.sh pause).</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>A: tests/test_main_offline.py::test_live_lands_before_the_call_and_advances_the_watermark_after_it (CALL index &lt; watermark index, lease released)
 and ::test_event_mode_calls_with_mode_event_and_never_touches_state; B2: tests/test_n8n_code.py asserts the watermark MERGE text and report_id; C: by reading
@@ -1457,25 +1509,30 @@
 payload contract to the B1 webhook (not implemented); HubSpot workflows on hot_flag_v1 replace Breeze "scheduled prompts" for alerts.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>None: the implementation writes tables; the caller renders the payload from new_deals_history + new_deals_runs (A) and delivers it (the B1 tail); C delivers nothing.</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Three delivery mechanisms (webhook tail, in-workflow tail, none) and an email is never idempotent: a re-trigger re-sends. A's
 watermark advances before the POST, so a failed delivery leaves rows in BigQuery and no later window re-sends them (B-G04, mitigated
 by retries + the run-status marker).</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>workflows/NEW_DEALS_DELIVERY.json accepts the same payload contract from any orchestrator; next iteration: deliver from
 new_deals_last_7d so a re-send is the same report whichever scenario filled the table (result_B open question, default yes).</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>build_workflow.py produces NEW_DEALS_DELIVERY.json with Header Auth, zero-row branch and lastNode response (read, --check up to date);
 main.py retry loop read. Email sent: not yet — first authenticated run (needs the SMTP credential in n8n).</t>
@@ -1514,25 +1571,30 @@
 writeback/bootstrap_property.sh.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>None: writeback/index.mjs reads the views (lane C).</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Only C writes to HubSpot. Blocked by scopes until a second private app with crm.objects.deals.write exists (C-G10) and the properties
 are created with a one-off crm.schemas.deals.write token. HubSpot's native BigQuery → HubSpot sync would be an alternative only on
 Data Hub Enterprise (C-G1, contested).</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>The job reads BigQuery views, not the orchestrator, so one deployment of writeback/ is the write-back for A, B2 and C alike; the
 delta view + writeback_log make it value-idempotent (f(f(x)) = f(x)) and safe under overlapping executions.</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>node --check writeback/index.mjs OK; DRYRUN=1 writeback/deploy_job.sh prints the job, binding and Scheduler commands; the 100-slice
 and 207 handling read against the HubSpot docs (result_C C-G7). Any PATCH: not yet — first authenticated run (and not before R35).</t>
@@ -1570,24 +1632,29 @@
 writeback_log, no HubSpot call (`writeback/deploy_job.sh execute`).</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>mode = 'dry': the batch is computed, ONE new_deals_runs row (dry_run TRUE, rows_written 0, counts and data_gaps filled) and nothing else — no MERGE, no history, no state. tests/pass3_batch_vectors.sql is the executed check of the read path in a dev dataset; `bq --dry_run` cannot execute a CALL, so `deploy.sh dry` (a real CALL with mode dry) is the gate.</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>A and B2 rehearse exactly Monday's window with zero writes; C's SQL half can only be rehearsed syntactically or against a dev dataset,
 because the scheduled script always MERGEs when it runs. The job half matches A's flag model (one env var opens the live path).</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Rehearse C's SQL in hubspot_dev (DATASET override in .env) before registering with auto-scheduling; keep the gate order dry → run →
 probe → enable on every surface (deploy.sh, scheduler.sh, scheduled_query.sh + deploy_job.sh live).</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>A: tests/test_main_offline.py::test_dry_lands_calls_with_mode_dry_and_touches_no_sink_or_state; B2 (retired): tests/test_n8n_code.py (dry_run true, rows_written 0) and the IF
 wiring in NEW_DEALS_FULL.json; C: DRYRUN=1 sql/scheduled_query.sh renders (bq --dry_run itself needs credentials: not yet — first
@@ -1624,25 +1691,30 @@
 run_ts = … then `gcloud run jobs execute`; sync backfill = DTS backfill run.</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>A CALL with the same (run_ts, entity, orchestrator) recomputes from the same slice and rewrites the same history and runs rows (events excepted: never replayed, never replaced); a re-landing replaces the slice (raw_slice_replaced — the predecessor is recoverable by time travel only); a replayed older run_time never rewinds C's watermark (GREATEST) and never overwrites a newer observation (the MERGE guard).</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Same rows after the replay when the replayed window is covered: A/B2 rewind one state row and re-run a watermark window; C re-executes
 run_time slices whose fixed 14-day lookback must span the gap (longer gaps need several run_times or a larger lookback_days). Deep
 replays in A/B2 are capped at 10,000 search results per query (G15, contested: decades of volume).</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Rewind in A/B2 is `deploy.sh replay`; in C choose start/end so consecutive run_times overlap (weekly run_times, 14-day lookback);
 the Equality check "after a second identical run" is the proof on every surface.</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>A: deploy.sh replay read (UPDATE then live), frozen set by tests/test_main_offline.py; B2: watermark/history SQL by
 tests/test_n8n_code.py; C: sql/scheduled_query.sh prints the replay command. Replayed: not yet — first authenticated run.</t>
@@ -1684,25 +1756,30 @@
 raw_landing_failed / raw_slice_replaced / labels_missing from its landing, the procedure labels_missing / dedup_horizon_partial.</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>The procedure writes the history slice and the runs row (OK with rows_written, duplicate_suspects, day1_hot, data_gaps; FAILED with @@error.message after a ROLLBACK, then RAISE; dry_run TRUE for a dry run); the gaps it decides: labels_missing, dedup_horizon_partial. The raw slices are the audit's inputs: `SELECT * FROM new_deals_batch_rows(X, …)` recomputes any past run without writing.</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Same two tables, same columns, one orchestrator value per surface, so one query answers "what ran, what landed" for all three;
 writeback_log exists only where a write-back exists (C's job). Per-surface extras (Cloud Logging, n8n executions, transfer-run
 history) are additive, not the record.</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>None needed for the tables; `deploy.sh probe` is the shared query. R44 (closed): new_deals_history now lives in bigquery_schema.sql, so
 `deploy.sh tables` creates it; sql/audit_tables.sql keeps writeback_log.</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>A: tests/test_main_offline.py (new_deals_runs row status OK orchestrator cloud-run-function; history load present); B2:
 tests/test_n8n_code.py ('n8n' in runlog_sql, IF(dry, 0, n)); C: SQL read; sql/apply.sh DRYRUN=1 renders audit_tables.sql (2 DDL).
@@ -1740,24 +1817,29 @@
 two HubSpot private apps (read for DTS/A, crm.objects.deals.write for the job) + a one-off crm.schemas.deals.write token.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>bigquery.routines.get + jobs.create to CALL; dataEditor on the dataset covers every table the procedure writes; nothing outside the dataset — no sync dataset, no HubSpot.</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>A and C are IAM-only (OIDC/OAuth, private surfaces); B exposes a public URL guarded by an application secret and holds a key and a token
 copy in its own database. Least privilege holds only if the write token never reaches A's function or n8n.</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Header Auth on every webhook (build_workflow.py CRED["header"]), token from Secret Manager (scheduler.sh reads it), separate write app
 pinned to the job (deploy_job.sh), the same DCL GRANT per identity; revisit IAP only with an IAP-aware Scheduler identity.</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Bindings read in deploy.sh invoker, deploy_n8n.sh, secrets.sh, deploy_job.sh (DRYRUN=1 prints them); NEW_DEALS_*.json webhooks carry
 authentication headerAuth (read). Policies applied: not yet — first authenticated run.</t>
@@ -1797,26 +1879,31 @@
 overlapping executions allowed — safe because the PATCH is value-idempotent and the delta view consults writeback_log first (C-G9).</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>One transaction per CALL over new_deals / new_deals_history / new_deals_runs / report_state: conflicting transactions are cancelled by the engine, so callers never share a minute (A's lease per entity, C's per-entity off-the-hour schedules); the lease check RAISEs for an advance_state caller while A holds the entity; CREATE OR REPLACE TEMP TABLE lets one script CALL twice; the handler's ROLLBACK is wrapped so a cancelled transaction still leaves its FAILED row.</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Three guards (lease + instance cap / n8n concurrency limit / transaction + idempotent PATCH). A's instance cap alone does not serialise
 a retry after a 504 and would 429 the second entity (G04, contested) — hence the lease and the offset schedules; B2 relies on the n8n
 process limit; C has no instance cap at all.</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Shared safety comes from the data model (MERGE + frozen columns + watermark-after-MERGE + value-idempotent PATCH), which every surface
 has. To match A exactly, B2 would add the lease UPDATE as a node before "HubSpot search" (open); C's job may add a weekly lease row in
 writeback_log (optional).</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>A: tests/test_main_offline.py::test_overlapping_run_gets_409_and_writes_nothing; B2: service.yaml values read; C: by reading the SQL and
 index.mjs. Under real retries: not yet — first authenticated run.</t>
@@ -1853,24 +1940,29 @@
 job's JSON summary line ({run_ts, patched, errors, dry}); SQL probes: new_deals_runs by entity/orchestrator and writeback_log by status.</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>new_deals_runs (status, error, duration_ms up to the transaction's opening, data_gaps), new_deals_history, deals_raw / labels_raw; the caller's log line; the job history (one query job per CALL, the procedure's statements as its child jobs in INFORMATION_SCHEMA.JOBS).</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Different consoles and log shapes; the ABORTED run row (stale sync) exists only in C, the delivery status only in A/B1, the n8n
 execution record only in B.</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>One documented bq probe set for all three — `deploy.sh probe` and `deploy.sh status` read tables every surface writes; add
 `SELECT status, COUNT(*) FROM writeback_log WHERE DATE(run_ts) = CURRENT_DATE() GROUP BY status` for C.</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Log formatter and probe SQL read; test output shows the JSON lines ("run complete", "run already in progress"). Logs in Cloud Logging:
 not yet — first authenticated run.</t>
@@ -1906,24 +1998,29 @@
 inside the free tier; third Scheduler job free (a fourth $0.10/month). HubSpot's native sync would need Data Hub Enterprise (not chosen).</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>One query job per CALL over kilobytes (the slice) plus the 90-day horizon scan of deals_raw (clustered by entity, deal_id, createdate; partitioned by run_ts, 730-day expiry); no runtime, no instance, no scale-to-zero question.</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>A and C scale to zero and stay inside free tiers; B carries an always-on database and either a sleeping instance (webhook variant) or an
 always-on one (Schedule Trigger variant). Preview pricing of the DTS connector may change at GA (C-G14).</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Keep B on the Scheduler → webhook variant (MIN_SCALE=0 in .env); accept the Cloud SQL floor as the price of the editor; re-check the
 billing export after the first month.</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Figures from result_B / result_C pricing lookups (2026-10-05); no bill yet — first month after the first authenticated run.</t>
         </is>
@@ -1940,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1949,9 +2046,10 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1987,15 +2085,20 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
+          <t>R · The raw root + the one SQL implementation (deals_raw / labels_raw → deals_landed_v1 → new_deals_batch_rows → new_deals_batch), CALLed by A after its landing and by C after its landing — pass 3 (2026-10-21); not a scenario but what every scenario executes — command</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
           <t>Parity</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Identical artefact to compare</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2026,17 +2129,22 @@
           <t>same .env; sql/apply.sh refuses placeholders in PROJECT SYNC_DATASET SYNC_DEALS_TABLE SYNC_OWNERS_TABLE; writeback/deploy_job.sh requires HUBSPOT_WRITE_TOKEN_VERSION</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>n/a — no settings of its own; the callers' .env (PROJECT, DATASET, PORTAL_ID) renders the four files</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>the echo line "project=… region=… dataset=… fn=… sa=… schedules: …" (A); rendered files without "${" (B, C)</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Same result when all three read the one .env copied from .env.example (they do). SYNC_* values exist only after C's first transfer run (R36).</t>
         </is>
@@ -2067,17 +2175,22 @@
           <t>n/a in scripts — bigquerydatatransfer.googleapis.com (scheduled queries, DTS) is not enabled by any script (R45)</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>bigquery.googleapis.com, already enabled by every lane</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>gcloud services list --enabled shows the APIs</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>Idempotent on every surface. C relies on the BigQuery Data Transfer API being already on.</t>
         </is>
@@ -2108,17 +2221,22 @@
           <t>sql/scheduled_query.sh — SA new-deals-sql (jobUser + DCL GRANT); writeback/deploy_job.sh deploy — SAs new-deals-writeback (jobUser + GRANT + secretAccessor) and new-deals-scheduler</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>the callers' SAs: dataEditor on the dataset (routines included) + jobUser — granted by deploy.sh iam / tables and by scheduled_query.sh</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>gcloud iam service-accounts list shows the SAs; gcloud projects get-iam-policy shows the bindings</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Five identities in all; only B needs a key (B-G10). Each script is describe-then-create.</t>
         </is>
@@ -2149,17 +2267,22 @@
           <t>sql/apply.sh — bigquery_schema.sql → audit_tables.sql (new_deals_history, writeback_log) → hot_score_v1.sql → deals_synced_v1.sql → hot_deals_v1.sql</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>deploy.sh tables + deploy.sh routines (or sql/apply.sh): deals_raw, labels_raw, new_deals_runs.data_gaps; hot_score_v1; deals_landed_v1 + new_deals_batch_rows; new_deals_batch — OR REPLACE, re-runnable</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>bq ls $PROJECT:hubspot lists report_state, new_deals, new_deals_runs, new_deals_history, writeback_log, hot_score_v1, the views</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>All DDL is IF NOT EXISTS / OR REPLACE. Until R44 is folded in, run sql/apply.sh (or audit_tables.sql) before the first live run of A or B2.</t>
         </is>
@@ -2190,17 +2313,22 @@
           <t>printf '%s' "$WRITE_TOKEN" | gcloud secrets create hubspot-token-write --data-file=- (manual; not scripted) then HUBSPOT_SCHEMA_TOKEN=… writeback/bootstrap_property.sh (one-off)</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>n/a — no secret</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>gcloud secrets versions list &lt;name&gt; shows an enabled version; HubSpot GET /crm/v3/properties/deals/hot_score_v1 → 200 (C)</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Tokens never pass through .env or git. C needs a second private app with crm.objects.deals.write (R35).</t>
         </is>
@@ -2235,17 +2363,22 @@
           <t>sql/sync_transfer.sh (first transfer) → fill SYNC_* in .env → sql/apply.sh → HUBSPOT_TOKEN=… sql/refresh_pipeline_labels.sh → DISABLE_SCHEDULE=1 sql/scheduled_query.sh → writeback/deploy_job.sh (WRITEBACK_APPROVE=0)</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>deploy.sh routines IS the deploy (DDL only, no runtime); nothing executes until a caller CALLs</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>A: revision Ready, URL printed; B: n8n URL printed, 3 workflows listed in the editor; C: 2 transfer configs new-deals-&lt;entity&gt;-C (no auto scheduling), job new-deals-writeback</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>A's canonical form (R05). B: publish/activate only after a manual test execution. C: the DTS connector decides the synced table names (R36).</t>
         </is>
@@ -2276,17 +2409,22 @@
           <t>writeback/deploy_job.sh deploy also binds roles/run.invoker for new-deals-scheduler@ on the job and creates Scheduler job new-deals-writeback (30 5 * * 1 Zurich, OAuth) — enabled, but the job stays DRY</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>n/a — no trigger of its own; the callers' triggers</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>gcloud scheduler jobs list --location $REGION shows the jobs (A/B PAUSED, C ENABLED); gcloud run services get-iam-policy $FN shows run.invoker for the SA</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>R02: without run.invoker Scheduler gets 403. Three auth mechanisms (OIDC / shared header / OAuth to jobs.run).</t>
         </is>
@@ -2317,17 +2455,22 @@
           <t>DRYRUN=1 sql/scheduled_query.sh (bq query --dry_run of both rendered scripts); writeback/deploy_job.sh execute with WRITEBACK_APPROVE=0 → writeback_log rows status DRY; optional full rehearsal in a hubspot_dev dataset</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>tests/pass3_batch_vectors.sql in a dev dataset (15 vectors through root → view → table function, every row ok = TRUE, slice dropped); then deploy.sh dry exercises the procedure's dry branch end to end (one runs row per entity, rows_written 0)</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>payload {report_id, run_timestamp, orchestrator, dry_run: true, window{watermark_in, query_start, query_end}, row_count, rows_written: 0, duplicate_suspects, day1_hot[], data_gaps[], rows[]} (A; since pass 3 also one new_deals_runs row with dry_run TRUE); bytes processed + DRY rows (C)</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>THE GATE before any LIVE row below. A's dry run exercises the whole SQL path (landing, table function, the procedure's dry branch), so a missing routine or a broken view fails here (B2 retired). C's SQL half has no compute-only mode; its dry run is syntax + the dev dataset.</t>
         </is>
@@ -2362,17 +2505,22 @@
           <t>bq mk --transfer_run --run_time=$(date -u +%FT%TZ) &lt;transfer config new-deals-SEALSQ-C&gt; (and ICALPS); then writeback/deploy_job.sh execute (still DRY until step 10)</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>the callers' first live runs: deploy.sh run SEALSQ (CALL with advance_state FALSE) and bq mk --transfer_run (CALL with advance_state TRUE on NEW_DEALS_&lt;entity&gt;_C); then the acceptance SQL of docs/PASS3_RAW_ROOT.md (every history row has its raw row; the JSON carries the property names; data_gaps per run)</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>rows_written == row_count; hubspot.new_deals holds the rows; report_state NEW_DEALS_&lt;entity&gt; (A) / NEW_DEALS_&lt;entity&gt;_C (C) watermark == run_timestamp; one new_deals_runs row per run (written by the procedure)</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>First run with no watermark looks back FIRST_RUN_DAYS=7 (A) / 14 days lookback (C). Re-running the same window writes nothing new (MERGE). Requires the routines (deploy.sh routines / sql/apply.sh) — a missing procedure fails the CALL (deploy.sh dry catches it).</t>
         </is>
@@ -2407,17 +2555,22 @@
           <t>sql/scheduled_query.sh without DISABLE_SCHEDULE (bq update --transfer_config re-enables auto scheduling); writeback/deploy_job.sh live (WRITEBACK_APPROVE=1 on the job)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>n/a — the callers' schedules</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>jobs ENABLED; gcloud scheduler jobs run new-deals-SEALSQ → HTTP 200 in the job log; C: transfer configs scheduled, job env WRITEBACK_APPROVE=1</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Only after step 8 passed on both entities and step 9 was probed. C's chain must keep its slack (per-entity, off-the-hour schedules); the procedure refuses to advance C's row while A holds the entity's lease.</t>
         </is>
@@ -2448,17 +2601,22 @@
           <t>same two bq queries; plus SELECT status, COUNT(*) FROM writeback_log WHERE DATE(run_ts) = CURRENT_DATE() GROUP BY status</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>SELECT * FROM new_deals_batch_rows(&lt;run_ts&gt;, '&lt;entity&gt;', '&lt;orchestrator&gt;', NULL) — what the rules make of a run's inputs now, without writing; SELECT run_ts, entity, orchestrator, status, rows_written, data_gaps FROM new_deals_runs ORDER BY run_ts DESC</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>the two result tables — identical from every scenario because every scenario writes the same dataset</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Paste the dated output verbatim into the Overview verdict and docs/EXECUTION_SURFACES.md after the first live run.</t>
         </is>
@@ -2489,17 +2647,22 @@
           <t>same bq query (rows NEW_DEALS_&lt;entity&gt;_C); bq ls --transfer_run &lt;config&gt;; gcloud run jobs executions list --job new-deals-writeback</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>SELECT orchestrator, entity, COUNT(*), MIN(createdate) FROM deals_raw WHERE run_ts &gt;= TIMESTAMP_SUB(CURRENT_TIMESTAMP(), INTERVAL 90 DAY) GROUP BY 1, 2 — the horizon the duplicate rule reads; dedup_horizon_partial on the latest runs row says whether it is full</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>one report_state row per entity per lane (A: NEW_DEALS_&lt;entity&gt;; C: _C); watermark == last successful run_timestamp; lock_until NULL between runs</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Where am I: the watermark is the checkpoint. The per-surface describe commands are additive.</t>
         </is>
@@ -2534,17 +2697,22 @@
           <t>bq mk --transfer_run --start_time=2026-09-28T04:00:00Z --end_time=2026-10-05T04:00:00Z &lt;config&gt;; HubSpot side: DELETE FROM writeback_log WHERE run_ts = … then gcloud run jobs execute new-deals-writeback</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>CALL new_deals_batch with the same run_ts over the same slice (idempotent rewrite); a transfer run with a past run_time re-lands the slice (raw_backfilled_from_current_sync); deploy.sh replay opens a NEW run_ts — it adds a slice, never replaces one</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>row count unchanged for an already-loaded window; last_seen_run advanced; day1_hot_score unchanged; a new new_deals_history slice per run_ts</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Backfill route (L12). Idempotent through the MERGE and the frozen set; C's lookback must cover the gap.</t>
         </is>
@@ -4647,7 +4815,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>B · n8n on Cloud Run (B1 delivery tail NEW_DEALS_DELIVERY.json; B2 — n8n owning the pipeline, NEW_DEALS_FULL.json — retired in pass 3 phase 3, decision D6; its cells record the design as built) / C · BigQuery compute (synced deals, hot_score_v1 UDF, scheduled script) + Node 22 write-back job; Breeze reads, Claude iterates — command</t>
+          <t>B · n8n on Cloud Run (B1 delivery tail NEW_DEALS_DELIVERY.json; B2 — n8n owning the pipeline, NEW_DEALS_FULL.json — retired in pass 3 phase 3, decision D6; its cells record the design as built) / C · BigQuery compute (synced deals, hot_score_v1 UDF, scheduled script) + Node 22 write-back job; Breeze reads, Claude iterates / R · The raw root + the one SQL implementation (deals_raw / labels_raw → deals_landed_v1 → new_deals_batch_rows → new_deals_batch), CALLed by A after its landing and by C after its landing — pass 3 (2026-10-21); not a scenario but what every scenario executes — command</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
